--- a/Cronograma/Itinerario_Manobanda_Jeffrey_V1.xlsx
+++ b/Cronograma/Itinerario_Manobanda_Jeffrey_V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. UNIVERSIDAD\Docuemntos-pasantias\31109_PPP\Cronograma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EA7031-C7A8-46A2-964C-6C42FC80E148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63FF3DC-810D-4AB4-A8D0-0F943209147F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -390,9 +390,6 @@
     <t>Verificar tenant-scope: datos aislados por tenant</t>
   </si>
   <si>
-    <t>Documentación técnica + Demo final</t>
-  </si>
-  <si>
     <t>Documentar todos los endpoints nuevos en README o API_DOCS.md</t>
   </si>
   <si>
@@ -856,6 +853,9 @@
   </si>
   <si>
     <t>Commit final + PR para merge a develop</t>
+  </si>
+  <si>
+    <t>Documentación técnica</t>
   </si>
 </sst>
 </file>
@@ -1566,7 +1566,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" s="13">
         <v>2</v>
@@ -1584,7 +1584,7 @@
       <c r="A10" s="32"/>
       <c r="B10" s="32"/>
       <c r="C10" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" s="13">
         <v>2</v>
@@ -1601,7 +1601,7 @@
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
       <c r="C11" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" s="13">
         <v>2</v>
@@ -1615,10 +1615,10 @@
         <v>46126</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D12" s="13">
         <v>2</v>
@@ -1636,7 +1636,7 @@
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D13" s="13">
         <v>2</v>
@@ -1652,7 +1652,7 @@
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
       <c r="C14" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D14" s="13">
         <v>2</v>
@@ -1667,10 +1667,10 @@
         <v>46127</v>
       </c>
       <c r="B15" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>125</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>126</v>
       </c>
       <c r="D15" s="13">
         <v>2</v>
@@ -1688,7 +1688,7 @@
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
       <c r="C16" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D16" s="13">
         <v>2</v>
@@ -1704,7 +1704,7 @@
       <c r="A17" s="23"/>
       <c r="B17" s="23"/>
       <c r="C17" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D17" s="13">
         <v>2</v>
@@ -1719,10 +1719,10 @@
         <v>46128</v>
       </c>
       <c r="B18" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>129</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>130</v>
       </c>
       <c r="D18" s="13">
         <v>2</v>
@@ -1740,7 +1740,7 @@
       <c r="A19" s="23"/>
       <c r="B19" s="23"/>
       <c r="C19" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D19" s="13">
         <v>2</v>
@@ -1756,7 +1756,7 @@
       <c r="A20" s="23"/>
       <c r="B20" s="23"/>
       <c r="C20" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D20" s="13">
         <v>2</v>
@@ -1771,10 +1771,10 @@
         <v>46129</v>
       </c>
       <c r="B21" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="D21" s="13">
         <v>2</v>
@@ -1792,7 +1792,7 @@
       <c r="A22" s="23"/>
       <c r="B22" s="23"/>
       <c r="C22" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D22" s="13">
         <v>2</v>
@@ -1808,7 +1808,7 @@
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
       <c r="C23" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D23" s="13">
         <v>2</v>
@@ -1823,10 +1823,10 @@
         <v>46132</v>
       </c>
       <c r="B24" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>137</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="D24" s="13">
         <v>2</v>
@@ -1844,7 +1844,7 @@
       <c r="A25" s="23"/>
       <c r="B25" s="23"/>
       <c r="C25" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D25" s="13">
         <v>2</v>
@@ -1860,7 +1860,7 @@
       <c r="A26" s="23"/>
       <c r="B26" s="23"/>
       <c r="C26" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D26" s="13">
         <v>2</v>
@@ -1875,10 +1875,10 @@
         <v>46133</v>
       </c>
       <c r="B27" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="D27" s="13">
         <v>2</v>
@@ -1896,7 +1896,7 @@
       <c r="A28" s="23"/>
       <c r="B28" s="23"/>
       <c r="C28" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D28" s="13">
         <v>2</v>
@@ -1912,7 +1912,7 @@
       <c r="A29" s="23"/>
       <c r="B29" s="23"/>
       <c r="C29" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D29" s="13">
         <v>2</v>
@@ -1927,10 +1927,10 @@
         <v>46134</v>
       </c>
       <c r="B30" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>146</v>
       </c>
       <c r="D30" s="13">
         <v>2</v>
@@ -1948,7 +1948,7 @@
       <c r="A31" s="23"/>
       <c r="B31" s="23"/>
       <c r="C31" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D31" s="13">
         <v>2</v>
@@ -1964,7 +1964,7 @@
       <c r="A32" s="23"/>
       <c r="B32" s="23"/>
       <c r="C32" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D32" s="13">
         <v>2</v>
@@ -1979,10 +1979,10 @@
         <v>46135</v>
       </c>
       <c r="B33" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>149</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>150</v>
       </c>
       <c r="D33" s="13">
         <v>2</v>
@@ -2000,7 +2000,7 @@
       <c r="A34" s="32"/>
       <c r="B34" s="32"/>
       <c r="C34" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D34" s="13">
         <v>2</v>
@@ -2016,7 +2016,7 @@
       <c r="A35" s="33"/>
       <c r="B35" s="33"/>
       <c r="C35" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D35" s="13">
         <v>2</v>
@@ -2031,10 +2031,10 @@
         <v>46136</v>
       </c>
       <c r="B36" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>153</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>154</v>
       </c>
       <c r="D36" s="13">
         <v>2</v>
@@ -2052,7 +2052,7 @@
       <c r="A37" s="23"/>
       <c r="B37" s="23"/>
       <c r="C37" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="11"/>
@@ -2064,7 +2064,7 @@
       <c r="A38" s="23"/>
       <c r="B38" s="23"/>
       <c r="C38" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D38" s="13">
         <v>2</v>
@@ -2081,10 +2081,10 @@
         <v>46139</v>
       </c>
       <c r="B39" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>157</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>158</v>
       </c>
       <c r="D39" s="13">
         <v>2</v>
@@ -2102,7 +2102,7 @@
       <c r="A40" s="23"/>
       <c r="B40" s="23"/>
       <c r="C40" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D40" s="13"/>
       <c r="E40" s="11"/>
@@ -2114,7 +2114,7 @@
       <c r="A41" s="23"/>
       <c r="B41" s="23"/>
       <c r="C41" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D41" s="13">
         <v>2</v>
@@ -2131,10 +2131,10 @@
         <v>46140</v>
       </c>
       <c r="B42" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>161</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>162</v>
       </c>
       <c r="D42" s="13">
         <v>2</v>
@@ -2152,7 +2152,7 @@
       <c r="A43" s="32"/>
       <c r="B43" s="32"/>
       <c r="C43" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D43" s="13">
         <v>2</v>
@@ -2168,7 +2168,7 @@
       <c r="A44" s="33"/>
       <c r="B44" s="33"/>
       <c r="C44" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D44" s="13">
         <v>2</v>
@@ -2183,10 +2183,10 @@
         <v>46141</v>
       </c>
       <c r="B45" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>165</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>166</v>
       </c>
       <c r="D45" s="13">
         <v>2</v>
@@ -2204,7 +2204,7 @@
       <c r="A46" s="23"/>
       <c r="B46" s="23"/>
       <c r="C46" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D46" s="13">
         <v>2</v>
@@ -2220,7 +2220,7 @@
       <c r="A47" s="23"/>
       <c r="B47" s="23"/>
       <c r="C47" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D47" s="13">
         <v>2</v>
@@ -2256,7 +2256,7 @@
       <c r="A49" s="23"/>
       <c r="B49" s="23"/>
       <c r="C49" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D49" s="21" t="s">
         <v>22</v>
@@ -3425,10 +3425,10 @@
         <v>46164</v>
       </c>
       <c r="B123" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="C123" s="13" t="s">
         <v>111</v>
-      </c>
-      <c r="C123" s="13" t="s">
-        <v>112</v>
       </c>
       <c r="D123" s="21" t="s">
         <v>22</v>
@@ -3446,7 +3446,7 @@
       <c r="A124" s="23"/>
       <c r="B124" s="32"/>
       <c r="C124" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D124" s="13">
         <v>1</v>
@@ -3460,7 +3460,7 @@
       <c r="A125" s="23"/>
       <c r="B125" s="32"/>
       <c r="C125" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D125" s="21" t="s">
         <v>23</v>
@@ -3476,7 +3476,7 @@
       <c r="A126" s="23"/>
       <c r="B126" s="32"/>
       <c r="C126" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D126" s="13">
         <v>1</v>
@@ -3490,7 +3490,7 @@
       <c r="A127" s="23"/>
       <c r="B127" s="32"/>
       <c r="C127" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D127" s="13">
         <v>1</v>
@@ -3504,7 +3504,7 @@
       <c r="A128" s="23"/>
       <c r="B128" s="33"/>
       <c r="C128" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D128" s="13">
         <v>1</v>
@@ -3519,10 +3519,10 @@
         <v>46168</v>
       </c>
       <c r="B129" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D129" s="13">
         <v>1</v>
@@ -3540,7 +3540,7 @@
       <c r="A130" s="23"/>
       <c r="B130" s="30"/>
       <c r="C130" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D130" s="13">
         <v>1</v>
@@ -3554,7 +3554,7 @@
       <c r="A131" s="23"/>
       <c r="B131" s="30"/>
       <c r="C131" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D131" s="21" t="s">
         <v>23</v>
@@ -3570,7 +3570,7 @@
       <c r="A132" s="23"/>
       <c r="B132" s="30"/>
       <c r="C132" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D132" s="21" t="s">
         <v>23</v>
@@ -3584,7 +3584,7 @@
       <c r="A133" s="23"/>
       <c r="B133" s="30"/>
       <c r="C133" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D133" s="21">
         <v>1</v>
@@ -3598,7 +3598,7 @@
       <c r="A134" s="23"/>
       <c r="B134" s="30"/>
       <c r="C134" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D134" s="21" t="s">
         <v>23</v>
@@ -3612,7 +3612,7 @@
       <c r="A135" s="23"/>
       <c r="B135" s="30"/>
       <c r="C135" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D135" s="21" t="s">
         <v>23</v>
@@ -3626,7 +3626,7 @@
       <c r="A136" s="23"/>
       <c r="B136" s="30"/>
       <c r="C136" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D136" s="21">
         <v>1</v>
@@ -3641,10 +3641,10 @@
         <v>46169</v>
       </c>
       <c r="B137" s="30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D137" s="13">
         <v>2</v>
@@ -3662,7 +3662,7 @@
       <c r="A138" s="23"/>
       <c r="B138" s="30"/>
       <c r="C138" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D138" s="21" t="s">
         <v>23</v>
@@ -3676,7 +3676,7 @@
       <c r="A139" s="23"/>
       <c r="B139" s="30"/>
       <c r="C139" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D139" s="21" t="s">
         <v>23</v>
@@ -3692,7 +3692,7 @@
       <c r="A140" s="23"/>
       <c r="B140" s="30"/>
       <c r="C140" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D140" s="13">
         <v>1</v>
@@ -3706,7 +3706,7 @@
       <c r="A141" s="23"/>
       <c r="B141" s="30"/>
       <c r="C141" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D141" s="13">
         <v>1</v>
@@ -3720,7 +3720,7 @@
       <c r="A142" s="23"/>
       <c r="B142" s="30"/>
       <c r="C142" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D142" s="13">
         <v>1</v>
@@ -3735,10 +3735,10 @@
         <v>46170</v>
       </c>
       <c r="B143" s="30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D143" s="13">
         <v>1</v>
@@ -3756,7 +3756,7 @@
       <c r="A144" s="23"/>
       <c r="B144" s="30"/>
       <c r="C144" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D144" s="21" t="s">
         <v>23</v>
@@ -3770,7 +3770,7 @@
       <c r="A145" s="23"/>
       <c r="B145" s="30"/>
       <c r="C145" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D145" s="21" t="s">
         <v>23</v>
@@ -3784,7 +3784,7 @@
       <c r="A146" s="23"/>
       <c r="B146" s="30"/>
       <c r="C146" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D146" s="13">
         <v>1</v>
@@ -3800,7 +3800,7 @@
       <c r="A147" s="23"/>
       <c r="B147" s="30"/>
       <c r="C147" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D147" s="13">
         <v>2</v>
@@ -3814,7 +3814,7 @@
       <c r="A148" s="23"/>
       <c r="B148" s="30"/>
       <c r="C148" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D148" s="21" t="s">
         <v>23</v>
@@ -3828,7 +3828,7 @@
       <c r="A149" s="23"/>
       <c r="B149" s="30"/>
       <c r="C149" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D149" s="21" t="s">
         <v>23</v>
@@ -3843,10 +3843,10 @@
         <v>46171</v>
       </c>
       <c r="B150" s="30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D150" s="13">
         <v>1</v>
@@ -3864,7 +3864,7 @@
       <c r="A151" s="23"/>
       <c r="B151" s="30"/>
       <c r="C151" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D151" s="13">
         <v>1</v>
@@ -3878,7 +3878,7 @@
       <c r="A152" s="23"/>
       <c r="B152" s="30"/>
       <c r="C152" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D152" s="21" t="s">
         <v>23</v>
@@ -3894,7 +3894,7 @@
       <c r="A153" s="23"/>
       <c r="B153" s="30"/>
       <c r="C153" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D153" s="21" t="s">
         <v>23</v>
@@ -3908,7 +3908,7 @@
       <c r="A154" s="23"/>
       <c r="B154" s="30"/>
       <c r="C154" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D154" s="13">
         <v>2</v>
@@ -3922,7 +3922,7 @@
       <c r="A155" s="23"/>
       <c r="B155" s="30"/>
       <c r="C155" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D155" s="13">
         <v>1</v>
@@ -3937,10 +3937,10 @@
         <v>46174</v>
       </c>
       <c r="B156" s="30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D156" s="21">
         <v>1</v>
@@ -3958,7 +3958,7 @@
       <c r="A157" s="23"/>
       <c r="B157" s="30"/>
       <c r="C157" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D157" s="21" t="s">
         <v>23</v>
@@ -3972,7 +3972,7 @@
       <c r="A158" s="23"/>
       <c r="B158" s="30"/>
       <c r="C158" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D158" s="21">
         <v>1</v>
@@ -3986,7 +3986,7 @@
       <c r="A159" s="23"/>
       <c r="B159" s="30"/>
       <c r="C159" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D159" s="21" t="s">
         <v>23</v>
@@ -4002,7 +4002,7 @@
       <c r="A160" s="23"/>
       <c r="B160" s="30"/>
       <c r="C160" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D160" s="21">
         <v>2</v>
@@ -4016,7 +4016,7 @@
       <c r="A161" s="23"/>
       <c r="B161" s="30"/>
       <c r="C161" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D161" s="21" t="s">
         <v>23</v>
@@ -4030,7 +4030,7 @@
       <c r="A162" s="23"/>
       <c r="B162" s="30"/>
       <c r="C162" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D162" s="21" t="s">
         <v>23</v>
@@ -4045,10 +4045,10 @@
         <v>46175</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C163" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D163" s="13">
         <v>1</v>
@@ -4066,7 +4066,7 @@
       <c r="A164" s="23"/>
       <c r="B164" s="35"/>
       <c r="C164" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D164" s="13">
         <v>1</v>
@@ -4080,7 +4080,7 @@
       <c r="A165" s="23"/>
       <c r="B165" s="35"/>
       <c r="C165" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D165" s="13">
         <v>1</v>
@@ -4096,7 +4096,7 @@
       <c r="A166" s="23"/>
       <c r="B166" s="35"/>
       <c r="C166" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D166" s="13">
         <v>2</v>
@@ -4110,7 +4110,7 @@
       <c r="A167" s="23"/>
       <c r="B167" s="35"/>
       <c r="C167" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D167" s="21" t="s">
         <v>23</v>
@@ -4124,7 +4124,7 @@
       <c r="A168" s="23"/>
       <c r="B168" s="35"/>
       <c r="C168" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D168" s="21" t="s">
         <v>23</v>
@@ -4139,10 +4139,10 @@
         <v>46176</v>
       </c>
       <c r="B169" s="30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C169" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D169" s="13">
         <v>1</v>
@@ -4160,7 +4160,7 @@
       <c r="A170" s="23"/>
       <c r="B170" s="30"/>
       <c r="C170" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D170" s="21" t="s">
         <v>22</v>
@@ -4174,7 +4174,7 @@
       <c r="A171" s="23"/>
       <c r="B171" s="30"/>
       <c r="C171" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D171" s="21" t="s">
         <v>23</v>
@@ -4190,7 +4190,7 @@
       <c r="A172" s="23"/>
       <c r="B172" s="30"/>
       <c r="C172" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D172" s="13">
         <v>1</v>
@@ -4204,7 +4204,7 @@
       <c r="A173" s="23"/>
       <c r="B173" s="30"/>
       <c r="C173" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D173" s="13">
         <v>1</v>
@@ -4218,7 +4218,7 @@
       <c r="A174" s="23"/>
       <c r="B174" s="30"/>
       <c r="C174" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D174" s="13">
         <v>1</v>
@@ -4233,10 +4233,10 @@
         <v>46177</v>
       </c>
       <c r="B175" s="30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C175" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D175" s="21" t="s">
         <v>22</v>
@@ -4254,7 +4254,7 @@
       <c r="A176" s="23"/>
       <c r="B176" s="30"/>
       <c r="C176" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D176" s="21" t="s">
         <v>22</v>
@@ -4270,7 +4270,7 @@
       <c r="A177" s="23"/>
       <c r="B177" s="30"/>
       <c r="C177" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D177" s="13">
         <v>1</v>
@@ -4284,7 +4284,7 @@
       <c r="A178" s="23"/>
       <c r="B178" s="30"/>
       <c r="C178" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D178" s="21" t="s">
         <v>22</v>
@@ -4298,7 +4298,7 @@
       <c r="A179" s="23"/>
       <c r="B179" s="30"/>
       <c r="C179" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D179" s="21" t="s">
         <v>23</v>
@@ -4313,10 +4313,10 @@
         <v>46178</v>
       </c>
       <c r="B180" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C180" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D180" s="13">
         <v>1</v>
@@ -4334,7 +4334,7 @@
       <c r="A181" s="23"/>
       <c r="B181" s="30"/>
       <c r="C181" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D181" s="21" t="s">
         <v>23</v>
@@ -4348,7 +4348,7 @@
       <c r="A182" s="23"/>
       <c r="B182" s="30"/>
       <c r="C182" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D182" s="21" t="s">
         <v>23</v>
@@ -4364,7 +4364,7 @@
       <c r="A183" s="23"/>
       <c r="B183" s="30"/>
       <c r="C183" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D183" s="13">
         <v>1</v>
@@ -4378,7 +4378,7 @@
       <c r="A184" s="23"/>
       <c r="B184" s="30"/>
       <c r="C184" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D184" s="13">
         <v>2</v>
@@ -4392,7 +4392,7 @@
       <c r="A185" s="23"/>
       <c r="B185" s="30"/>
       <c r="C185" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D185" s="13">
         <v>1</v>
@@ -4407,10 +4407,10 @@
         <v>46181</v>
       </c>
       <c r="B186" s="30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C186" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D186" s="13">
         <v>1</v>
@@ -4428,7 +4428,7 @@
       <c r="A187" s="23"/>
       <c r="B187" s="30"/>
       <c r="C187" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D187" s="21" t="s">
         <v>22</v>
@@ -4442,7 +4442,7 @@
       <c r="A188" s="23"/>
       <c r="B188" s="30"/>
       <c r="C188" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D188" s="21" t="s">
         <v>23</v>
@@ -4458,7 +4458,7 @@
       <c r="A189" s="23"/>
       <c r="B189" s="30"/>
       <c r="C189" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D189" s="13">
         <v>2</v>
@@ -4472,7 +4472,7 @@
       <c r="A190" s="23"/>
       <c r="B190" s="30"/>
       <c r="C190" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D190" s="13">
         <v>1</v>
@@ -4487,10 +4487,10 @@
         <v>46182</v>
       </c>
       <c r="B191" s="30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C191" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D191" s="13">
         <v>1</v>
@@ -4508,7 +4508,7 @@
       <c r="A192" s="23"/>
       <c r="B192" s="30"/>
       <c r="C192" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D192" s="21">
         <v>1</v>
@@ -4522,7 +4522,7 @@
       <c r="A193" s="23"/>
       <c r="B193" s="30"/>
       <c r="C193" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D193" s="21">
         <v>1</v>
@@ -4536,7 +4536,7 @@
       <c r="A194" s="23"/>
       <c r="B194" s="30"/>
       <c r="C194" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D194" s="21" t="s">
         <v>23</v>
@@ -4552,7 +4552,7 @@
       <c r="A195" s="23"/>
       <c r="B195" s="30"/>
       <c r="C195" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D195" s="21">
         <v>1</v>
@@ -4566,7 +4566,7 @@
       <c r="A196" s="23"/>
       <c r="B196" s="30"/>
       <c r="C196" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D196" s="13">
         <v>1</v>
@@ -4580,7 +4580,7 @@
       <c r="A197" s="23"/>
       <c r="B197" s="30"/>
       <c r="C197" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D197" s="21" t="s">
         <v>23</v>
@@ -4595,10 +4595,10 @@
         <v>46183</v>
       </c>
       <c r="B198" s="30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C198" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D198" s="13">
         <v>1</v>
@@ -4616,7 +4616,7 @@
       <c r="A199" s="23"/>
       <c r="B199" s="30"/>
       <c r="C199" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D199" s="13">
         <v>1</v>
@@ -4630,7 +4630,7 @@
       <c r="A200" s="23"/>
       <c r="B200" s="30"/>
       <c r="C200" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D200" s="21" t="s">
         <v>23</v>
@@ -4646,7 +4646,7 @@
       <c r="A201" s="23"/>
       <c r="B201" s="30"/>
       <c r="C201" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D201" s="21" t="s">
         <v>23</v>
@@ -4660,7 +4660,7 @@
       <c r="A202" s="23"/>
       <c r="B202" s="30"/>
       <c r="C202" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D202" s="13">
         <v>2</v>
@@ -4674,7 +4674,7 @@
       <c r="A203" s="23"/>
       <c r="B203" s="30"/>
       <c r="C203" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D203" s="13">
         <v>1</v>
@@ -4689,10 +4689,10 @@
         <v>46184</v>
       </c>
       <c r="B204" s="30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D204" s="13">
         <v>2</v>
@@ -4710,7 +4710,7 @@
       <c r="A205" s="23"/>
       <c r="B205" s="30"/>
       <c r="C205" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D205" s="13">
         <v>1</v>
@@ -4726,7 +4726,7 @@
       <c r="A206" s="23"/>
       <c r="B206" s="30"/>
       <c r="C206" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D206" s="13">
         <v>3</v>
@@ -4741,10 +4741,10 @@
         <v>46185</v>
       </c>
       <c r="B207" s="30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C207" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D207" s="21" t="s">
         <v>22</v>
@@ -4762,7 +4762,7 @@
       <c r="A208" s="23"/>
       <c r="B208" s="30"/>
       <c r="C208" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D208" s="21">
         <v>1</v>
@@ -4776,7 +4776,7 @@
       <c r="A209" s="23"/>
       <c r="B209" s="30"/>
       <c r="C209" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D209" s="21" t="s">
         <v>23</v>
@@ -4790,7 +4790,7 @@
       <c r="A210" s="23"/>
       <c r="B210" s="30"/>
       <c r="C210" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D210" s="13">
         <v>1</v>
@@ -4806,7 +4806,7 @@
       <c r="A211" s="23"/>
       <c r="B211" s="30"/>
       <c r="C211" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D211" s="13">
         <v>1</v>
@@ -4820,7 +4820,7 @@
       <c r="A212" s="23"/>
       <c r="B212" s="30"/>
       <c r="C212" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D212" s="13">
         <v>1</v>

--- a/Cronograma/Itinerario_Manobanda_Jeffrey_V1.xlsx
+++ b/Cronograma/Itinerario_Manobanda_Jeffrey_V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. UNIVERSIDAD\Docuemntos-pasantias\31109_PPP\Cronograma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63FF3DC-810D-4AB4-A8D0-0F943209147F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41C5955-D564-4DC6-9DE7-5F1D349EC1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1071,7 +1071,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1137,7 +1137,16 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1149,17 +1158,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1173,23 +1176,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1483,15 +1469,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.7">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A2" s="4" t="s">
@@ -1559,10 +1545,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="49.5" x14ac:dyDescent="0.5">
-      <c r="A9" s="31">
+      <c r="A9" s="32">
         <v>46125</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="32" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="13" t="s">
@@ -1572,17 +1558,17 @@
         <v>2</v>
       </c>
       <c r="E9" s="12"/>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="23">
         <v>6</v>
       </c>
       <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:8" ht="49.5" x14ac:dyDescent="0.5">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="13" t="s">
         <v>119</v>
       </c>
@@ -1593,28 +1579,28 @@
         <f>SUM(D9:D11)</f>
         <v>6</v>
       </c>
-      <c r="F10" s="25"/>
-      <c r="G10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="49.5" x14ac:dyDescent="0.5">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="13" t="s">
         <v>120</v>
       </c>
       <c r="D11" s="13">
         <v>2</v>
       </c>
-      <c r="F11" s="26"/>
-      <c r="G11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A12" s="23">
+      <c r="A12" s="30">
         <v>46126</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="30" t="s">
         <v>117</v>
       </c>
       <c r="C12" s="13" t="s">
@@ -1624,17 +1610,17 @@
         <v>2</v>
       </c>
       <c r="E12" s="11"/>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="23">
         <v>6</v>
       </c>
       <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="13" t="s">
         <v>122</v>
       </c>
@@ -1644,13 +1630,13 @@
       <c r="E13" s="12">
         <v>6</v>
       </c>
-      <c r="F13" s="25"/>
-      <c r="G13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="11"/>
     </row>
     <row r="14" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
       <c r="C14" s="13" t="s">
         <v>123</v>
       </c>
@@ -1658,15 +1644,15 @@
         <v>2</v>
       </c>
       <c r="E14" s="12"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="11"/>
     </row>
     <row r="15" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A15" s="23">
+      <c r="A15" s="30">
         <v>46127</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="30" t="s">
         <v>124</v>
       </c>
       <c r="C15" s="13" t="s">
@@ -1676,17 +1662,17 @@
         <v>2</v>
       </c>
       <c r="E15" s="11"/>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="23">
         <v>6</v>
       </c>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="13" t="s">
         <v>126</v>
       </c>
@@ -1696,13 +1682,13 @@
       <c r="E16" s="12">
         <v>6</v>
       </c>
-      <c r="F16" s="25"/>
-      <c r="G16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
       <c r="C17" s="13" t="s">
         <v>127</v>
       </c>
@@ -1710,15 +1696,15 @@
         <v>2</v>
       </c>
       <c r="E17" s="12"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="11"/>
     </row>
     <row r="18" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A18" s="23">
+      <c r="A18" s="30">
         <v>46128</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="30" t="s">
         <v>128</v>
       </c>
       <c r="C18" s="13" t="s">
@@ -1728,17 +1714,17 @@
         <v>2</v>
       </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="23">
         <v>6</v>
       </c>
       <c r="H18" s="11"/>
     </row>
     <row r="19" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="13" t="s">
         <v>130</v>
       </c>
@@ -1748,13 +1734,13 @@
       <c r="E19" s="12">
         <v>6</v>
       </c>
-      <c r="F19" s="25"/>
-      <c r="G19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="13" t="s">
         <v>131</v>
       </c>
@@ -1762,15 +1748,15 @@
         <v>2</v>
       </c>
       <c r="E20" s="12"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="25"/>
       <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A21" s="23">
+      <c r="A21" s="30">
         <v>46129</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="30" t="s">
         <v>132</v>
       </c>
       <c r="C21" s="13" t="s">
@@ -1780,17 +1766,17 @@
         <v>2</v>
       </c>
       <c r="E21" s="11"/>
-      <c r="F21" s="24" t="s">
+      <c r="F21" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="23">
         <v>6</v>
       </c>
       <c r="H21" s="11"/>
     </row>
     <row r="22" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="13" t="s">
         <v>134</v>
       </c>
@@ -1800,13 +1786,13 @@
       <c r="E22" s="12">
         <v>6</v>
       </c>
-      <c r="F22" s="25"/>
-      <c r="G22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="12"/>
     </row>
     <row r="23" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="13" t="s">
         <v>135</v>
       </c>
@@ -1814,15 +1800,15 @@
         <v>2</v>
       </c>
       <c r="E23" s="12"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="25"/>
       <c r="H23" s="11"/>
     </row>
     <row r="24" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A24" s="23">
+      <c r="A24" s="30">
         <v>46132</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="30" t="s">
         <v>136</v>
       </c>
       <c r="C24" s="13" t="s">
@@ -1832,17 +1818,17 @@
         <v>2</v>
       </c>
       <c r="E24" s="11"/>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="23">
         <v>6</v>
       </c>
       <c r="H24" s="11"/>
     </row>
     <row r="25" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="30"/>
       <c r="C25" s="13" t="s">
         <v>138</v>
       </c>
@@ -1852,13 +1838,13 @@
       <c r="E25" s="12">
         <v>6</v>
       </c>
-      <c r="F25" s="25"/>
-      <c r="G25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="24"/>
       <c r="H25" s="12"/>
     </row>
     <row r="26" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
       <c r="C26" s="13" t="s">
         <v>139</v>
       </c>
@@ -1866,15 +1852,15 @@
         <v>2</v>
       </c>
       <c r="E26" s="12"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="25"/>
       <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A27" s="23">
+      <c r="A27" s="30">
         <v>46133</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="30" t="s">
         <v>140</v>
       </c>
       <c r="C27" s="13" t="s">
@@ -1884,17 +1870,17 @@
         <v>2</v>
       </c>
       <c r="E27" s="11"/>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="23">
         <v>6</v>
       </c>
       <c r="H27" s="11"/>
     </row>
     <row r="28" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
       <c r="C28" s="13" t="s">
         <v>142</v>
       </c>
@@ -1904,13 +1890,13 @@
       <c r="E28" s="12">
         <v>6</v>
       </c>
-      <c r="F28" s="25"/>
-      <c r="G28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="24"/>
       <c r="H28" s="11"/>
     </row>
     <row r="29" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
       <c r="C29" s="13" t="s">
         <v>143</v>
       </c>
@@ -1918,15 +1904,15 @@
         <v>2</v>
       </c>
       <c r="E29" s="12"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="25"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A30" s="23">
+      <c r="A30" s="30">
         <v>46134</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="30" t="s">
         <v>144</v>
       </c>
       <c r="C30" s="13" t="s">
@@ -1936,17 +1922,17 @@
         <v>2</v>
       </c>
       <c r="E30" s="11"/>
-      <c r="F30" s="24" t="s">
+      <c r="F30" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="23">
         <v>6</v>
       </c>
       <c r="H30" s="11"/>
     </row>
     <row r="31" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="30"/>
       <c r="C31" s="13" t="s">
         <v>146</v>
       </c>
@@ -1956,13 +1942,13 @@
       <c r="E31" s="12">
         <v>6</v>
       </c>
-      <c r="F31" s="25"/>
-      <c r="G31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="24"/>
       <c r="H31" s="12"/>
     </row>
     <row r="32" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
       <c r="C32" s="13" t="s">
         <v>147</v>
       </c>
@@ -1970,15 +1956,15 @@
         <v>2</v>
       </c>
       <c r="E32" s="12"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="25"/>
       <c r="H32" s="12"/>
     </row>
     <row r="33" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A33" s="31">
+      <c r="A33" s="32">
         <v>46135</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="32" t="s">
         <v>148</v>
       </c>
       <c r="C33" s="13" t="s">
@@ -1988,17 +1974,17 @@
         <v>2</v>
       </c>
       <c r="E33" s="11"/>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G33" s="27">
+      <c r="G33" s="23">
         <v>6</v>
       </c>
       <c r="H33" s="11"/>
     </row>
     <row r="34" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="13" t="s">
         <v>150</v>
       </c>
@@ -2008,13 +1994,13 @@
       <c r="E34" s="12">
         <v>6</v>
       </c>
-      <c r="F34" s="25"/>
-      <c r="G34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="24"/>
       <c r="H34" s="12"/>
     </row>
     <row r="35" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A35" s="33"/>
-      <c r="B35" s="33"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="13" t="s">
         <v>151</v>
       </c>
@@ -2022,15 +2008,15 @@
         <v>2</v>
       </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="25"/>
       <c r="H35" s="11"/>
     </row>
     <row r="36" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A36" s="23">
+      <c r="A36" s="30">
         <v>46136</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="B36" s="30" t="s">
         <v>152</v>
       </c>
       <c r="C36" s="13" t="s">
@@ -2040,29 +2026,29 @@
         <v>2</v>
       </c>
       <c r="E36" s="11"/>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G36" s="27">
+      <c r="G36" s="23">
         <v>6</v>
       </c>
       <c r="H36" s="11"/>
     </row>
     <row r="37" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A37" s="23"/>
-      <c r="B37" s="23"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
       <c r="C37" s="13" t="s">
         <v>154</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="24"/>
       <c r="H37" s="11"/>
     </row>
     <row r="38" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
       <c r="C38" s="13" t="s">
         <v>155</v>
       </c>
@@ -2072,15 +2058,15 @@
       <c r="E38" s="12">
         <v>6</v>
       </c>
-      <c r="F38" s="26"/>
-      <c r="G38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="25"/>
       <c r="H38" s="12"/>
     </row>
     <row r="39" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A39" s="23">
+      <c r="A39" s="30">
         <v>46139</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="30" t="s">
         <v>156</v>
       </c>
       <c r="C39" s="13" t="s">
@@ -2090,29 +2076,29 @@
         <v>2</v>
       </c>
       <c r="E39" s="11"/>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G39" s="27">
+      <c r="G39" s="23">
         <v>6</v>
       </c>
       <c r="H39" s="11"/>
     </row>
     <row r="40" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
       <c r="C40" s="13" t="s">
         <v>158</v>
       </c>
       <c r="D40" s="13"/>
       <c r="E40" s="11"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="24"/>
       <c r="H40" s="11"/>
     </row>
     <row r="41" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A41" s="23"/>
-      <c r="B41" s="23"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
       <c r="C41" s="13" t="s">
         <v>159</v>
       </c>
@@ -2122,15 +2108,15 @@
       <c r="E41" s="12">
         <v>6</v>
       </c>
-      <c r="F41" s="26"/>
-      <c r="G41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="25"/>
       <c r="H41" s="12"/>
     </row>
     <row r="42" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A42" s="31">
+      <c r="A42" s="32">
         <v>46140</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="32" t="s">
         <v>160</v>
       </c>
       <c r="C42" s="13" t="s">
@@ -2140,17 +2126,17 @@
         <v>2</v>
       </c>
       <c r="E42" s="12"/>
-      <c r="F42" s="24" t="s">
+      <c r="F42" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G42" s="30">
+      <c r="G42" s="26">
         <v>6</v>
       </c>
       <c r="H42" s="11"/>
     </row>
     <row r="43" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A43" s="32"/>
-      <c r="B43" s="32"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="33"/>
       <c r="C43" s="13" t="s">
         <v>162</v>
       </c>
@@ -2160,13 +2146,13 @@
       <c r="E43" s="12">
         <v>6</v>
       </c>
-      <c r="F43" s="25"/>
-      <c r="G43" s="30"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="26"/>
       <c r="H43" s="11"/>
     </row>
     <row r="44" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A44" s="33"/>
-      <c r="B44" s="33"/>
+      <c r="A44" s="34"/>
+      <c r="B44" s="34"/>
       <c r="C44" s="13" t="s">
         <v>163</v>
       </c>
@@ -2174,15 +2160,15 @@
         <v>2</v>
       </c>
       <c r="E44" s="12"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="30"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="26"/>
       <c r="H44" s="12"/>
     </row>
     <row r="45" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A45" s="23">
+      <c r="A45" s="30">
         <v>46141</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="30" t="s">
         <v>164</v>
       </c>
       <c r="C45" s="13" t="s">
@@ -2192,17 +2178,17 @@
         <v>2</v>
       </c>
       <c r="E45" s="12"/>
-      <c r="F45" s="24" t="s">
+      <c r="F45" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G45" s="27">
+      <c r="G45" s="23">
         <v>6</v>
       </c>
       <c r="H45" s="11"/>
     </row>
     <row r="46" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
       <c r="C46" s="13" t="s">
         <v>166</v>
       </c>
@@ -2212,13 +2198,13 @@
       <c r="E46" s="12">
         <v>6</v>
       </c>
-      <c r="F46" s="25"/>
-      <c r="G46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="24"/>
       <c r="H46" s="11"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A47" s="23"/>
-      <c r="B47" s="23"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
       <c r="C47" s="13" t="s">
         <v>167</v>
       </c>
@@ -2226,15 +2212,15 @@
         <v>2</v>
       </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="25"/>
       <c r="H47" s="12"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A48" s="23">
+      <c r="A48" s="30">
         <v>46146</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="30" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="13" t="s">
@@ -2244,17 +2230,17 @@
         <v>1</v>
       </c>
       <c r="E48" s="11"/>
-      <c r="F48" s="24" t="s">
+      <c r="F48" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G48" s="27">
+      <c r="G48" s="23">
         <v>6</v>
       </c>
       <c r="H48" s="11"/>
     </row>
     <row r="49" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A49" s="23"/>
-      <c r="B49" s="23"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
       <c r="C49" s="13" t="s">
         <v>168</v>
       </c>
@@ -2262,13 +2248,13 @@
         <v>22</v>
       </c>
       <c r="E49" s="11"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="24"/>
       <c r="H49" s="12"/>
     </row>
     <row r="50" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A50" s="23"/>
-      <c r="B50" s="23"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="30"/>
       <c r="C50" s="13" t="s">
         <v>25</v>
       </c>
@@ -2278,13 +2264,13 @@
       <c r="E50" s="12">
         <v>6</v>
       </c>
-      <c r="F50" s="25"/>
-      <c r="G50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="24"/>
       <c r="H50" s="12"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A51" s="23"/>
-      <c r="B51" s="23"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
       <c r="C51" s="13" t="s">
         <v>26</v>
       </c>
@@ -2292,13 +2278,13 @@
         <v>1</v>
       </c>
       <c r="E51" s="11"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="24"/>
       <c r="H51" s="12"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A52" s="23"/>
-      <c r="B52" s="23"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="30"/>
       <c r="C52" s="13" t="s">
         <v>27</v>
       </c>
@@ -2306,13 +2292,13 @@
         <v>1</v>
       </c>
       <c r="E52" s="12"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="24"/>
       <c r="H52" s="11"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A53" s="23"/>
-      <c r="B53" s="23"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="13" t="s">
         <v>28</v>
       </c>
@@ -2320,15 +2306,15 @@
         <v>23</v>
       </c>
       <c r="E53" s="12"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="25"/>
       <c r="H53" s="11"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A54" s="23">
+      <c r="A54" s="30">
         <v>46147</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="30" t="s">
         <v>29</v>
       </c>
       <c r="C54" s="13" t="s">
@@ -2338,17 +2324,17 @@
         <v>1</v>
       </c>
       <c r="E54" s="11"/>
-      <c r="F54" s="24" t="s">
+      <c r="F54" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G54" s="27">
+      <c r="G54" s="23">
         <v>6</v>
       </c>
       <c r="H54" s="12"/>
     </row>
     <row r="55" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A55" s="23"/>
-      <c r="B55" s="23"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="13" t="s">
         <v>30</v>
       </c>
@@ -2356,13 +2342,13 @@
         <v>2</v>
       </c>
       <c r="E55" s="11"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="24"/>
       <c r="H55" s="12"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A56" s="23"/>
-      <c r="B56" s="23"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="13" t="s">
         <v>31</v>
       </c>
@@ -2372,13 +2358,13 @@
       <c r="E56" s="12">
         <v>6</v>
       </c>
-      <c r="F56" s="25"/>
-      <c r="G56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="24"/>
       <c r="H56" s="12"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A57" s="23"/>
-      <c r="B57" s="23"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
       <c r="C57" s="13" t="s">
         <v>32</v>
       </c>
@@ -2386,13 +2372,13 @@
         <v>1</v>
       </c>
       <c r="E57" s="12"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="24"/>
       <c r="H57" s="11"/>
     </row>
     <row r="58" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A58" s="23"/>
-      <c r="B58" s="23"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="30"/>
       <c r="C58" s="13" t="s">
         <v>34</v>
       </c>
@@ -2400,15 +2386,15 @@
         <v>23</v>
       </c>
       <c r="E58" s="12"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="25"/>
       <c r="H58" s="11"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A59" s="23">
+      <c r="A59" s="30">
         <v>46148</v>
       </c>
-      <c r="B59" s="23" t="s">
+      <c r="B59" s="30" t="s">
         <v>35</v>
       </c>
       <c r="C59" s="13" t="s">
@@ -2418,17 +2404,17 @@
         <v>1</v>
       </c>
       <c r="E59" s="11"/>
-      <c r="F59" s="24" t="s">
+      <c r="F59" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G59" s="27">
+      <c r="G59" s="23">
         <v>6</v>
       </c>
       <c r="H59" s="11"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A60" s="23"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="30"/>
       <c r="C60" s="13" t="s">
         <v>37</v>
       </c>
@@ -2436,13 +2422,13 @@
         <v>22</v>
       </c>
       <c r="E60" s="11"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="24"/>
       <c r="H60" s="12"/>
     </row>
     <row r="61" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A61" s="23"/>
-      <c r="B61" s="23"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
       <c r="C61" s="13" t="s">
         <v>38</v>
       </c>
@@ -2452,13 +2438,13 @@
       <c r="E61" s="12">
         <v>6</v>
       </c>
-      <c r="F61" s="25"/>
-      <c r="G61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="24"/>
       <c r="H61" s="12"/>
     </row>
     <row r="62" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A62" s="23"/>
-      <c r="B62" s="23"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
       <c r="C62" s="13" t="s">
         <v>39</v>
       </c>
@@ -2466,13 +2452,13 @@
         <v>1</v>
       </c>
       <c r="E62" s="11"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="24"/>
       <c r="H62" s="12"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A63" s="23"/>
-      <c r="B63" s="23"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
       <c r="C63" s="13" t="s">
         <v>40</v>
       </c>
@@ -2480,13 +2466,13 @@
         <v>1</v>
       </c>
       <c r="E63" s="12"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="24"/>
       <c r="H63" s="11"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="30"/>
+      <c r="B64" s="30"/>
       <c r="C64" s="13" t="s">
         <v>41</v>
       </c>
@@ -2494,15 +2480,15 @@
         <v>23</v>
       </c>
       <c r="E64" s="12"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="29"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="25"/>
       <c r="H64" s="11"/>
     </row>
     <row r="65" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A65" s="23">
+      <c r="A65" s="30">
         <v>46149</v>
       </c>
-      <c r="B65" s="23" t="s">
+      <c r="B65" s="30" t="s">
         <v>42</v>
       </c>
       <c r="C65" s="13" t="s">
@@ -2512,17 +2498,17 @@
         <v>22</v>
       </c>
       <c r="E65" s="11"/>
-      <c r="F65" s="24" t="s">
+      <c r="F65" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G65" s="27">
+      <c r="G65" s="23">
         <v>6</v>
       </c>
       <c r="H65" s="12"/>
     </row>
     <row r="66" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A66" s="23"/>
-      <c r="B66" s="23"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="30"/>
       <c r="C66" s="13" t="s">
         <v>44</v>
       </c>
@@ -2530,13 +2516,13 @@
         <v>1</v>
       </c>
       <c r="E66" s="11"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="24"/>
       <c r="H66" s="11"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A67" s="23"/>
-      <c r="B67" s="23"/>
+      <c r="A67" s="30"/>
+      <c r="B67" s="30"/>
       <c r="C67" s="13" t="s">
         <v>45</v>
       </c>
@@ -2546,13 +2532,13 @@
       <c r="E67" s="12">
         <v>6</v>
       </c>
-      <c r="F67" s="25"/>
-      <c r="G67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="24"/>
       <c r="H67" s="11"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A68" s="23"/>
-      <c r="B68" s="23"/>
+      <c r="A68" s="30"/>
+      <c r="B68" s="30"/>
       <c r="C68" s="13" t="s">
         <v>46</v>
       </c>
@@ -2560,13 +2546,13 @@
         <v>1</v>
       </c>
       <c r="E68" s="11"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="24"/>
       <c r="H68" s="11"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A69" s="23"/>
-      <c r="B69" s="23"/>
+      <c r="A69" s="30"/>
+      <c r="B69" s="30"/>
       <c r="C69" s="13" t="s">
         <v>47</v>
       </c>
@@ -2574,13 +2560,13 @@
         <v>23</v>
       </c>
       <c r="E69" s="11"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="24"/>
       <c r="H69" s="11"/>
     </row>
     <row r="70" spans="1:8" ht="49.5" x14ac:dyDescent="0.5">
-      <c r="A70" s="23"/>
-      <c r="B70" s="23"/>
+      <c r="A70" s="30"/>
+      <c r="B70" s="30"/>
       <c r="C70" s="13" t="s">
         <v>48</v>
       </c>
@@ -2588,13 +2574,13 @@
         <v>23</v>
       </c>
       <c r="E70" s="11"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="24"/>
       <c r="H70" s="11"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A71" s="23"/>
-      <c r="B71" s="23"/>
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
       <c r="C71" s="13" t="s">
         <v>49</v>
       </c>
@@ -2602,15 +2588,15 @@
         <v>1</v>
       </c>
       <c r="E71" s="12"/>
-      <c r="F71" s="26"/>
-      <c r="G71" s="29"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="25"/>
       <c r="H71" s="11"/>
     </row>
     <row r="72" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A72" s="23">
+      <c r="A72" s="30">
         <v>46150</v>
       </c>
-      <c r="B72" s="23" t="s">
+      <c r="B72" s="30" t="s">
         <v>50</v>
       </c>
       <c r="C72" s="13" t="s">
@@ -2620,17 +2606,17 @@
         <v>22</v>
       </c>
       <c r="E72" s="11"/>
-      <c r="F72" s="24" t="s">
+      <c r="F72" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G72" s="27">
+      <c r="G72" s="23">
         <v>6</v>
       </c>
       <c r="H72" s="12"/>
     </row>
     <row r="73" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A73" s="23"/>
-      <c r="B73" s="23"/>
+      <c r="A73" s="30"/>
+      <c r="B73" s="30"/>
       <c r="C73" s="13" t="s">
         <v>52</v>
       </c>
@@ -2638,13 +2624,13 @@
         <v>1</v>
       </c>
       <c r="E73" s="11"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="24"/>
       <c r="H73" s="12"/>
     </row>
     <row r="74" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A74" s="23"/>
-      <c r="B74" s="23"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="30"/>
       <c r="C74" s="13" t="s">
         <v>53</v>
       </c>
@@ -2654,13 +2640,13 @@
       <c r="E74" s="12">
         <v>6</v>
       </c>
-      <c r="F74" s="25"/>
-      <c r="G74" s="28"/>
+      <c r="F74" s="28"/>
+      <c r="G74" s="24"/>
       <c r="H74" s="11"/>
     </row>
     <row r="75" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A75" s="23"/>
-      <c r="B75" s="23"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="30"/>
       <c r="C75" s="13" t="s">
         <v>54</v>
       </c>
@@ -2668,13 +2654,13 @@
         <v>1</v>
       </c>
       <c r="E75" s="11"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="24"/>
       <c r="H75" s="11"/>
     </row>
     <row r="76" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A76" s="23"/>
-      <c r="B76" s="23"/>
+      <c r="A76" s="30"/>
+      <c r="B76" s="30"/>
       <c r="C76" s="13" t="s">
         <v>55</v>
       </c>
@@ -2682,15 +2668,15 @@
         <v>23</v>
       </c>
       <c r="E76" s="12"/>
-      <c r="F76" s="26"/>
-      <c r="G76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="25"/>
       <c r="H76" s="11"/>
     </row>
     <row r="77" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A77" s="23">
+      <c r="A77" s="30">
         <v>46153</v>
       </c>
-      <c r="B77" s="23" t="s">
+      <c r="B77" s="30" t="s">
         <v>56</v>
       </c>
       <c r="C77" s="13" t="s">
@@ -2700,17 +2686,17 @@
         <v>22</v>
       </c>
       <c r="E77" s="11"/>
-      <c r="F77" s="24" t="s">
+      <c r="F77" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G77" s="27">
+      <c r="G77" s="23">
         <v>6</v>
       </c>
       <c r="H77" s="12"/>
     </row>
     <row r="78" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A78" s="23"/>
-      <c r="B78" s="23"/>
+      <c r="A78" s="30"/>
+      <c r="B78" s="30"/>
       <c r="C78" s="13" t="s">
         <v>58</v>
       </c>
@@ -2718,13 +2704,13 @@
         <v>2</v>
       </c>
       <c r="E78" s="11"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="24"/>
       <c r="H78" s="12"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A79" s="23"/>
-      <c r="B79" s="23"/>
+      <c r="A79" s="30"/>
+      <c r="B79" s="30"/>
       <c r="C79" s="13" t="s">
         <v>59</v>
       </c>
@@ -2734,13 +2720,13 @@
       <c r="E79" s="12">
         <v>6</v>
       </c>
-      <c r="F79" s="25"/>
-      <c r="G79" s="28"/>
+      <c r="F79" s="28"/>
+      <c r="G79" s="24"/>
       <c r="H79" s="11"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A80" s="23"/>
-      <c r="B80" s="23"/>
+      <c r="A80" s="30"/>
+      <c r="B80" s="30"/>
       <c r="C80" s="13" t="s">
         <v>60</v>
       </c>
@@ -2748,13 +2734,13 @@
         <v>23</v>
       </c>
       <c r="E80" s="11"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="28"/>
+      <c r="F80" s="28"/>
+      <c r="G80" s="24"/>
       <c r="H80" s="11"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A81" s="23"/>
-      <c r="B81" s="23"/>
+      <c r="A81" s="30"/>
+      <c r="B81" s="30"/>
       <c r="C81" s="13" t="s">
         <v>61</v>
       </c>
@@ -2762,13 +2748,13 @@
         <v>23</v>
       </c>
       <c r="E81" s="11"/>
-      <c r="F81" s="25"/>
-      <c r="G81" s="28"/>
+      <c r="F81" s="28"/>
+      <c r="G81" s="24"/>
       <c r="H81" s="11"/>
     </row>
     <row r="82" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A82" s="23"/>
-      <c r="B82" s="23"/>
+      <c r="A82" s="30"/>
+      <c r="B82" s="30"/>
       <c r="C82" s="13" t="s">
         <v>62</v>
       </c>
@@ -2776,15 +2762,15 @@
         <v>1</v>
       </c>
       <c r="E82" s="12"/>
-      <c r="F82" s="26"/>
-      <c r="G82" s="29"/>
+      <c r="F82" s="29"/>
+      <c r="G82" s="25"/>
       <c r="H82" s="12"/>
     </row>
     <row r="83" spans="1:8" ht="66" x14ac:dyDescent="0.5">
-      <c r="A83" s="23">
+      <c r="A83" s="30">
         <v>46154</v>
       </c>
-      <c r="B83" s="23" t="s">
+      <c r="B83" s="30" t="s">
         <v>63</v>
       </c>
       <c r="C83" s="13" t="s">
@@ -2794,17 +2780,17 @@
         <v>2</v>
       </c>
       <c r="E83" s="11"/>
-      <c r="F83" s="24" t="s">
+      <c r="F83" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G83" s="27">
+      <c r="G83" s="23">
         <v>6</v>
       </c>
       <c r="H83" s="11"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A84" s="23"/>
-      <c r="B84" s="23"/>
+      <c r="A84" s="30"/>
+      <c r="B84" s="30"/>
       <c r="C84" s="13" t="s">
         <v>65</v>
       </c>
@@ -2814,13 +2800,13 @@
       <c r="E84" s="12">
         <v>6</v>
       </c>
-      <c r="F84" s="25"/>
-      <c r="G84" s="28"/>
+      <c r="F84" s="28"/>
+      <c r="G84" s="24"/>
       <c r="H84" s="11"/>
     </row>
     <row r="85" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A85" s="23"/>
-      <c r="B85" s="23"/>
+      <c r="A85" s="30"/>
+      <c r="B85" s="30"/>
       <c r="C85" s="13" t="s">
         <v>66</v>
       </c>
@@ -2828,13 +2814,13 @@
         <v>1</v>
       </c>
       <c r="E85" s="11"/>
-      <c r="F85" s="25"/>
-      <c r="G85" s="28"/>
+      <c r="F85" s="28"/>
+      <c r="G85" s="24"/>
       <c r="H85" s="11"/>
     </row>
     <row r="86" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A86" s="23"/>
-      <c r="B86" s="23"/>
+      <c r="A86" s="30"/>
+      <c r="B86" s="30"/>
       <c r="C86" s="13" t="s">
         <v>67</v>
       </c>
@@ -2842,13 +2828,13 @@
         <v>1</v>
       </c>
       <c r="E86" s="11"/>
-      <c r="F86" s="25"/>
-      <c r="G86" s="28"/>
+      <c r="F86" s="28"/>
+      <c r="G86" s="24"/>
       <c r="H86" s="12"/>
     </row>
     <row r="87" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A87" s="23"/>
-      <c r="B87" s="23"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="30"/>
       <c r="C87" s="13" t="s">
         <v>68</v>
       </c>
@@ -2856,15 +2842,15 @@
         <v>1</v>
       </c>
       <c r="E87" s="12"/>
-      <c r="F87" s="26"/>
-      <c r="G87" s="29"/>
+      <c r="F87" s="29"/>
+      <c r="G87" s="25"/>
       <c r="H87" s="11"/>
     </row>
     <row r="88" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A88" s="23">
+      <c r="A88" s="30">
         <v>46155</v>
       </c>
-      <c r="B88" s="23" t="s">
+      <c r="B88" s="30" t="s">
         <v>69</v>
       </c>
       <c r="C88" s="13" t="s">
@@ -2874,17 +2860,17 @@
         <v>1</v>
       </c>
       <c r="E88" s="11"/>
-      <c r="F88" s="24" t="s">
+      <c r="F88" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G88" s="27">
+      <c r="G88" s="23">
         <v>6</v>
       </c>
       <c r="H88" s="11"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A89" s="23"/>
-      <c r="B89" s="23"/>
+      <c r="A89" s="30"/>
+      <c r="B89" s="30"/>
       <c r="C89" s="13" t="s">
         <v>71</v>
       </c>
@@ -2892,13 +2878,13 @@
         <v>23</v>
       </c>
       <c r="E89" s="11"/>
-      <c r="F89" s="25"/>
-      <c r="G89" s="28"/>
+      <c r="F89" s="28"/>
+      <c r="G89" s="24"/>
       <c r="H89" s="11"/>
     </row>
     <row r="90" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A90" s="23"/>
-      <c r="B90" s="23"/>
+      <c r="A90" s="30"/>
+      <c r="B90" s="30"/>
       <c r="C90" s="13" t="s">
         <v>72</v>
       </c>
@@ -2908,13 +2894,13 @@
       <c r="E90" s="12">
         <v>6</v>
       </c>
-      <c r="F90" s="25"/>
-      <c r="G90" s="28"/>
+      <c r="F90" s="28"/>
+      <c r="G90" s="24"/>
       <c r="H90" s="11"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A91" s="23"/>
-      <c r="B91" s="23"/>
+      <c r="A91" s="30"/>
+      <c r="B91" s="30"/>
       <c r="C91" s="13" t="s">
         <v>73</v>
       </c>
@@ -2922,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="E91" s="11"/>
-      <c r="F91" s="25"/>
-      <c r="G91" s="28"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="24"/>
       <c r="H91" s="11"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A92" s="23"/>
-      <c r="B92" s="23"/>
+      <c r="A92" s="30"/>
+      <c r="B92" s="30"/>
       <c r="C92" s="13" t="s">
         <v>74</v>
       </c>
@@ -2936,13 +2922,13 @@
         <v>23</v>
       </c>
       <c r="E92" s="12"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="24"/>
       <c r="H92" s="12"/>
     </row>
     <row r="93" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A93" s="23"/>
-      <c r="B93" s="23"/>
+      <c r="A93" s="30"/>
+      <c r="B93" s="30"/>
       <c r="C93" s="13" t="s">
         <v>75</v>
       </c>
@@ -2950,15 +2936,15 @@
         <v>23</v>
       </c>
       <c r="E93" s="12"/>
-      <c r="F93" s="26"/>
-      <c r="G93" s="29"/>
+      <c r="F93" s="29"/>
+      <c r="G93" s="25"/>
       <c r="H93" s="11"/>
     </row>
     <row r="94" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A94" s="23">
+      <c r="A94" s="30">
         <v>46156</v>
       </c>
-      <c r="B94" s="30" t="s">
+      <c r="B94" s="26" t="s">
         <v>76</v>
       </c>
       <c r="C94" s="13" t="s">
@@ -2968,17 +2954,17 @@
         <v>2</v>
       </c>
       <c r="E94" s="12"/>
-      <c r="F94" s="24" t="s">
+      <c r="F94" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G94" s="27">
+      <c r="G94" s="23">
         <v>6</v>
       </c>
       <c r="H94" s="12"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A95" s="23"/>
-      <c r="B95" s="30"/>
+      <c r="A95" s="30"/>
+      <c r="B95" s="26"/>
       <c r="C95" s="13" t="s">
         <v>78</v>
       </c>
@@ -2988,13 +2974,13 @@
       <c r="E95" s="12">
         <v>6</v>
       </c>
-      <c r="F95" s="25"/>
-      <c r="G95" s="28"/>
+      <c r="F95" s="28"/>
+      <c r="G95" s="24"/>
       <c r="H95" s="12"/>
     </row>
     <row r="96" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A96" s="23"/>
-      <c r="B96" s="30"/>
+      <c r="A96" s="30"/>
+      <c r="B96" s="26"/>
       <c r="C96" s="13" t="s">
         <v>79</v>
       </c>
@@ -3002,13 +2988,13 @@
         <v>22</v>
       </c>
       <c r="E96" s="12"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="28"/>
+      <c r="F96" s="28"/>
+      <c r="G96" s="24"/>
       <c r="H96" s="12"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A97" s="23"/>
-      <c r="B97" s="30"/>
+      <c r="A97" s="30"/>
+      <c r="B97" s="26"/>
       <c r="C97" s="13" t="s">
         <v>80</v>
       </c>
@@ -3016,15 +3002,15 @@
         <v>23</v>
       </c>
       <c r="E97" s="12"/>
-      <c r="F97" s="26"/>
-      <c r="G97" s="29"/>
+      <c r="F97" s="29"/>
+      <c r="G97" s="25"/>
       <c r="H97" s="11"/>
     </row>
     <row r="98" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A98" s="23">
+      <c r="A98" s="30">
         <v>46157</v>
       </c>
-      <c r="B98" s="23" t="s">
+      <c r="B98" s="30" t="s">
         <v>81</v>
       </c>
       <c r="C98" s="13" t="s">
@@ -3034,17 +3020,17 @@
         <v>22</v>
       </c>
       <c r="E98" s="12"/>
-      <c r="F98" s="24" t="s">
+      <c r="F98" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G98" s="27">
+      <c r="G98" s="23">
         <v>6</v>
       </c>
       <c r="H98" s="11"/>
     </row>
     <row r="99" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A99" s="23"/>
-      <c r="B99" s="23"/>
+      <c r="A99" s="30"/>
+      <c r="B99" s="30"/>
       <c r="C99" s="13" t="s">
         <v>83</v>
       </c>
@@ -3052,13 +3038,13 @@
         <v>1</v>
       </c>
       <c r="E99" s="12"/>
-      <c r="F99" s="25"/>
-      <c r="G99" s="28"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="24"/>
       <c r="H99" s="11"/>
     </row>
     <row r="100" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A100" s="23"/>
-      <c r="B100" s="23"/>
+      <c r="A100" s="30"/>
+      <c r="B100" s="30"/>
       <c r="C100" s="13" t="s">
         <v>84</v>
       </c>
@@ -3068,13 +3054,13 @@
       <c r="E100" s="12">
         <v>6</v>
       </c>
-      <c r="F100" s="25"/>
-      <c r="G100" s="28"/>
+      <c r="F100" s="28"/>
+      <c r="G100" s="24"/>
       <c r="H100" s="11"/>
     </row>
     <row r="101" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A101" s="23"/>
-      <c r="B101" s="23"/>
+      <c r="A101" s="30"/>
+      <c r="B101" s="30"/>
       <c r="C101" s="13" t="s">
         <v>85</v>
       </c>
@@ -3082,13 +3068,13 @@
         <v>1</v>
       </c>
       <c r="E101" s="12"/>
-      <c r="F101" s="25"/>
-      <c r="G101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="24"/>
       <c r="H101" s="11"/>
     </row>
     <row r="102" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A102" s="23"/>
-      <c r="B102" s="23"/>
+      <c r="A102" s="30"/>
+      <c r="B102" s="30"/>
       <c r="C102" s="13" t="s">
         <v>86</v>
       </c>
@@ -3096,13 +3082,13 @@
         <v>23</v>
       </c>
       <c r="E102" s="12"/>
-      <c r="F102" s="25"/>
-      <c r="G102" s="28"/>
+      <c r="F102" s="28"/>
+      <c r="G102" s="24"/>
       <c r="H102" s="11"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A103" s="23"/>
-      <c r="B103" s="23"/>
+      <c r="A103" s="30"/>
+      <c r="B103" s="30"/>
       <c r="C103" s="13" t="s">
         <v>87</v>
       </c>
@@ -3110,15 +3096,15 @@
         <v>1</v>
       </c>
       <c r="E103" s="12"/>
-      <c r="F103" s="26"/>
-      <c r="G103" s="29"/>
+      <c r="F103" s="29"/>
+      <c r="G103" s="25"/>
       <c r="H103" s="12"/>
     </row>
     <row r="104" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A104" s="23">
+      <c r="A104" s="30">
         <v>46160</v>
       </c>
-      <c r="B104" s="23" t="s">
+      <c r="B104" s="30" t="s">
         <v>88</v>
       </c>
       <c r="C104" s="13" t="s">
@@ -3128,17 +3114,17 @@
         <v>1</v>
       </c>
       <c r="E104" s="12"/>
-      <c r="F104" s="24" t="s">
+      <c r="F104" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G104" s="27">
+      <c r="G104" s="23">
         <v>6</v>
       </c>
       <c r="H104" s="11"/>
     </row>
     <row r="105" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A105" s="23"/>
-      <c r="B105" s="23"/>
+      <c r="A105" s="30"/>
+      <c r="B105" s="30"/>
       <c r="C105" s="13" t="s">
         <v>90</v>
       </c>
@@ -3146,13 +3132,13 @@
         <v>1</v>
       </c>
       <c r="E105" s="12"/>
-      <c r="F105" s="25"/>
-      <c r="G105" s="28"/>
+      <c r="F105" s="28"/>
+      <c r="G105" s="24"/>
       <c r="H105" s="11"/>
     </row>
     <row r="106" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A106" s="23"/>
-      <c r="B106" s="23"/>
+      <c r="A106" s="30"/>
+      <c r="B106" s="30"/>
       <c r="C106" s="13" t="s">
         <v>91</v>
       </c>
@@ -3162,13 +3148,13 @@
       <c r="E106" s="12">
         <v>6</v>
       </c>
-      <c r="F106" s="25"/>
-      <c r="G106" s="28"/>
+      <c r="F106" s="28"/>
+      <c r="G106" s="24"/>
       <c r="H106" s="11"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A107" s="23"/>
-      <c r="B107" s="23"/>
+      <c r="A107" s="30"/>
+      <c r="B107" s="30"/>
       <c r="C107" s="13" t="s">
         <v>92</v>
       </c>
@@ -3176,13 +3162,13 @@
         <v>1</v>
       </c>
       <c r="E107" s="12"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="28"/>
+      <c r="F107" s="28"/>
+      <c r="G107" s="24"/>
       <c r="H107" s="11"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A108" s="23"/>
-      <c r="B108" s="23"/>
+      <c r="A108" s="30"/>
+      <c r="B108" s="30"/>
       <c r="C108" s="13" t="s">
         <v>93</v>
       </c>
@@ -3190,13 +3176,13 @@
         <v>1</v>
       </c>
       <c r="E108" s="12"/>
-      <c r="F108" s="25"/>
-      <c r="G108" s="28"/>
+      <c r="F108" s="28"/>
+      <c r="G108" s="24"/>
       <c r="H108" s="11"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A109" s="23"/>
-      <c r="B109" s="23"/>
+      <c r="A109" s="30"/>
+      <c r="B109" s="30"/>
       <c r="C109" s="13" t="s">
         <v>94</v>
       </c>
@@ -3204,15 +3190,15 @@
         <v>23</v>
       </c>
       <c r="E109" s="12"/>
-      <c r="F109" s="26"/>
-      <c r="G109" s="29"/>
+      <c r="F109" s="29"/>
+      <c r="G109" s="25"/>
       <c r="H109" s="11"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A110" s="23">
+      <c r="A110" s="30">
         <v>46161</v>
       </c>
-      <c r="B110" s="23" t="s">
+      <c r="B110" s="30" t="s">
         <v>95</v>
       </c>
       <c r="C110" s="13" t="s">
@@ -3222,17 +3208,17 @@
         <v>2</v>
       </c>
       <c r="E110" s="12"/>
-      <c r="F110" s="24" t="s">
+      <c r="F110" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G110" s="27">
+      <c r="G110" s="23">
         <v>6</v>
       </c>
       <c r="H110" s="12"/>
     </row>
     <row r="111" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A111" s="23"/>
-      <c r="B111" s="23"/>
+      <c r="A111" s="30"/>
+      <c r="B111" s="30"/>
       <c r="C111" s="13" t="s">
         <v>97</v>
       </c>
@@ -3242,13 +3228,13 @@
       <c r="E111" s="12">
         <v>6</v>
       </c>
-      <c r="F111" s="25"/>
-      <c r="G111" s="28"/>
+      <c r="F111" s="28"/>
+      <c r="G111" s="24"/>
       <c r="H111" s="11"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A112" s="23"/>
-      <c r="B112" s="23"/>
+      <c r="A112" s="30"/>
+      <c r="B112" s="30"/>
       <c r="C112" s="13" t="s">
         <v>98</v>
       </c>
@@ -3256,13 +3242,13 @@
         <v>22</v>
       </c>
       <c r="E112" s="12"/>
-      <c r="F112" s="25"/>
-      <c r="G112" s="28"/>
+      <c r="F112" s="28"/>
+      <c r="G112" s="24"/>
       <c r="H112" s="11"/>
     </row>
     <row r="113" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A113" s="23"/>
-      <c r="B113" s="23"/>
+      <c r="A113" s="30"/>
+      <c r="B113" s="30"/>
       <c r="C113" s="13" t="s">
         <v>99</v>
       </c>
@@ -3270,15 +3256,15 @@
         <v>1</v>
       </c>
       <c r="E113" s="12"/>
-      <c r="F113" s="26"/>
-      <c r="G113" s="29"/>
+      <c r="F113" s="29"/>
+      <c r="G113" s="25"/>
       <c r="H113" s="12"/>
     </row>
     <row r="114" spans="1:8" ht="66" x14ac:dyDescent="0.5">
-      <c r="A114" s="23">
+      <c r="A114" s="30">
         <v>46162</v>
       </c>
-      <c r="B114" s="23" t="s">
+      <c r="B114" s="30" t="s">
         <v>100</v>
       </c>
       <c r="C114" s="13" t="s">
@@ -3288,17 +3274,17 @@
         <v>2</v>
       </c>
       <c r="E114" s="12"/>
-      <c r="F114" s="24" t="s">
+      <c r="F114" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G114" s="27">
+      <c r="G114" s="23">
         <v>6</v>
       </c>
       <c r="H114" s="11"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A115" s="23"/>
-      <c r="B115" s="23"/>
+      <c r="A115" s="30"/>
+      <c r="B115" s="30"/>
       <c r="C115" s="13" t="s">
         <v>102</v>
       </c>
@@ -3308,13 +3294,13 @@
       <c r="E115" s="12">
         <v>6</v>
       </c>
-      <c r="F115" s="25"/>
-      <c r="G115" s="28"/>
+      <c r="F115" s="28"/>
+      <c r="G115" s="24"/>
       <c r="H115" s="11"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A116" s="23"/>
-      <c r="B116" s="23"/>
+      <c r="A116" s="30"/>
+      <c r="B116" s="30"/>
       <c r="C116" s="13" t="s">
         <v>103</v>
       </c>
@@ -3322,13 +3308,13 @@
         <v>22</v>
       </c>
       <c r="E116" s="12"/>
-      <c r="F116" s="25"/>
-      <c r="G116" s="28"/>
+      <c r="F116" s="28"/>
+      <c r="G116" s="24"/>
       <c r="H116" s="11"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A117" s="23"/>
-      <c r="B117" s="23"/>
+      <c r="A117" s="30"/>
+      <c r="B117" s="30"/>
       <c r="C117" s="13" t="s">
         <v>104</v>
       </c>
@@ -3336,15 +3322,15 @@
         <v>23</v>
       </c>
       <c r="E117" s="12"/>
-      <c r="F117" s="26"/>
-      <c r="G117" s="29"/>
+      <c r="F117" s="29"/>
+      <c r="G117" s="25"/>
       <c r="H117" s="12"/>
     </row>
     <row r="118" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A118" s="23">
+      <c r="A118" s="30">
         <v>46163</v>
       </c>
-      <c r="B118" s="30" t="s">
+      <c r="B118" s="26" t="s">
         <v>105</v>
       </c>
       <c r="C118" s="13" t="s">
@@ -3354,17 +3340,17 @@
         <v>2</v>
       </c>
       <c r="E118" s="11"/>
-      <c r="F118" s="24" t="s">
+      <c r="F118" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G118" s="27">
+      <c r="G118" s="23">
         <v>6</v>
       </c>
       <c r="H118" s="11"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A119" s="23"/>
-      <c r="B119" s="30"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="26"/>
       <c r="C119" s="13" t="s">
         <v>107</v>
       </c>
@@ -3372,13 +3358,13 @@
         <v>1</v>
       </c>
       <c r="E119" s="11"/>
-      <c r="F119" s="25"/>
-      <c r="G119" s="28"/>
+      <c r="F119" s="28"/>
+      <c r="G119" s="24"/>
       <c r="H119" s="11"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A120" s="23"/>
-      <c r="B120" s="30"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="26"/>
       <c r="C120" s="13" t="s">
         <v>108</v>
       </c>
@@ -3388,13 +3374,13 @@
       <c r="E120" s="12">
         <v>6</v>
       </c>
-      <c r="F120" s="25"/>
-      <c r="G120" s="28"/>
+      <c r="F120" s="28"/>
+      <c r="G120" s="24"/>
       <c r="H120" s="11"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A121" s="23"/>
-      <c r="B121" s="30"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="26"/>
       <c r="C121" s="13" t="s">
         <v>109</v>
       </c>
@@ -3402,13 +3388,13 @@
         <v>23</v>
       </c>
       <c r="E121" s="11"/>
-      <c r="F121" s="25"/>
-      <c r="G121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="24"/>
       <c r="H121" s="11"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A122" s="23"/>
-      <c r="B122" s="30"/>
+      <c r="A122" s="30"/>
+      <c r="B122" s="26"/>
       <c r="C122" s="13" t="s">
         <v>110</v>
       </c>
@@ -3416,15 +3402,15 @@
         <v>23</v>
       </c>
       <c r="E122" s="12"/>
-      <c r="F122" s="26"/>
-      <c r="G122" s="29"/>
+      <c r="F122" s="29"/>
+      <c r="G122" s="25"/>
       <c r="H122" s="11"/>
     </row>
     <row r="123" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A123" s="23">
+      <c r="A123" s="30">
         <v>46164</v>
       </c>
-      <c r="B123" s="31" t="s">
+      <c r="B123" s="32" t="s">
         <v>266</v>
       </c>
       <c r="C123" s="13" t="s">
@@ -3434,17 +3420,17 @@
         <v>22</v>
       </c>
       <c r="E123" s="11"/>
-      <c r="F123" s="24" t="s">
+      <c r="F123" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G123" s="27">
+      <c r="G123" s="23">
         <v>6</v>
       </c>
       <c r="H123" s="12"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A124" s="23"/>
-      <c r="B124" s="32"/>
+      <c r="A124" s="30"/>
+      <c r="B124" s="33"/>
       <c r="C124" s="13" t="s">
         <v>112</v>
       </c>
@@ -3452,13 +3438,13 @@
         <v>1</v>
       </c>
       <c r="E124" s="11"/>
-      <c r="F124" s="25"/>
-      <c r="G124" s="28"/>
+      <c r="F124" s="28"/>
+      <c r="G124" s="24"/>
       <c r="H124" s="12"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A125" s="23"/>
-      <c r="B125" s="32"/>
+      <c r="A125" s="30"/>
+      <c r="B125" s="33"/>
       <c r="C125" s="13" t="s">
         <v>113</v>
       </c>
@@ -3468,13 +3454,13 @@
       <c r="E125" s="12">
         <v>6</v>
       </c>
-      <c r="F125" s="25"/>
-      <c r="G125" s="28"/>
+      <c r="F125" s="28"/>
+      <c r="G125" s="24"/>
       <c r="H125" s="12"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A126" s="23"/>
-      <c r="B126" s="32"/>
+      <c r="A126" s="30"/>
+      <c r="B126" s="33"/>
       <c r="C126" s="13" t="s">
         <v>114</v>
       </c>
@@ -3482,13 +3468,13 @@
         <v>1</v>
       </c>
       <c r="E126" s="11"/>
-      <c r="F126" s="25"/>
-      <c r="G126" s="28"/>
+      <c r="F126" s="28"/>
+      <c r="G126" s="24"/>
       <c r="H126" s="12"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A127" s="23"/>
-      <c r="B127" s="32"/>
+      <c r="A127" s="30"/>
+      <c r="B127" s="33"/>
       <c r="C127" s="13" t="s">
         <v>115</v>
       </c>
@@ -3496,13 +3482,13 @@
         <v>1</v>
       </c>
       <c r="E127" s="11"/>
-      <c r="F127" s="25"/>
-      <c r="G127" s="28"/>
+      <c r="F127" s="28"/>
+      <c r="G127" s="24"/>
       <c r="H127" s="12"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A128" s="23"/>
-      <c r="B128" s="33"/>
+      <c r="A128" s="30"/>
+      <c r="B128" s="34"/>
       <c r="C128" s="13" t="s">
         <v>116</v>
       </c>
@@ -3510,15 +3496,15 @@
         <v>1</v>
       </c>
       <c r="E128" s="12"/>
-      <c r="F128" s="26"/>
-      <c r="G128" s="29"/>
+      <c r="F128" s="29"/>
+      <c r="G128" s="25"/>
       <c r="H128" s="11"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A129" s="23">
+      <c r="A129" s="30">
         <v>46168</v>
       </c>
-      <c r="B129" s="30" t="s">
+      <c r="B129" s="26" t="s">
         <v>169</v>
       </c>
       <c r="C129" s="13" t="s">
@@ -3528,17 +3514,17 @@
         <v>1</v>
       </c>
       <c r="E129" s="11"/>
-      <c r="F129" s="24" t="s">
+      <c r="F129" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G129" s="27">
+      <c r="G129" s="23">
         <v>6</v>
       </c>
       <c r="H129" s="12"/>
     </row>
-    <row r="130" spans="1:8" s="36" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A130" s="23"/>
-      <c r="B130" s="30"/>
+    <row r="130" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A130" s="30"/>
+      <c r="B130" s="26"/>
       <c r="C130" s="13" t="s">
         <v>184</v>
       </c>
@@ -3546,13 +3532,13 @@
         <v>1</v>
       </c>
       <c r="E130" s="11"/>
-      <c r="F130" s="25"/>
-      <c r="G130" s="28"/>
+      <c r="F130" s="28"/>
+      <c r="G130" s="24"/>
       <c r="H130" s="12"/>
     </row>
-    <row r="131" spans="1:8" s="36" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A131" s="23"/>
-      <c r="B131" s="30"/>
+    <row r="131" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A131" s="30"/>
+      <c r="B131" s="26"/>
       <c r="C131" s="13" t="s">
         <v>185</v>
       </c>
@@ -3562,13 +3548,13 @@
       <c r="E131" s="12">
         <v>6</v>
       </c>
-      <c r="F131" s="25"/>
-      <c r="G131" s="28"/>
+      <c r="F131" s="28"/>
+      <c r="G131" s="24"/>
       <c r="H131" s="12"/>
     </row>
-    <row r="132" spans="1:8" s="36" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A132" s="23"/>
-      <c r="B132" s="30"/>
+    <row r="132" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A132" s="30"/>
+      <c r="B132" s="26"/>
       <c r="C132" s="13" t="s">
         <v>186</v>
       </c>
@@ -3576,13 +3562,13 @@
         <v>23</v>
       </c>
       <c r="E132" s="11"/>
-      <c r="F132" s="25"/>
-      <c r="G132" s="28"/>
+      <c r="F132" s="28"/>
+      <c r="G132" s="24"/>
       <c r="H132" s="12"/>
     </row>
-    <row r="133" spans="1:8" s="36" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A133" s="23"/>
-      <c r="B133" s="30"/>
+    <row r="133" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A133" s="30"/>
+      <c r="B133" s="26"/>
       <c r="C133" s="13" t="s">
         <v>187</v>
       </c>
@@ -3590,13 +3576,13 @@
         <v>1</v>
       </c>
       <c r="E133" s="11"/>
-      <c r="F133" s="25"/>
-      <c r="G133" s="28"/>
+      <c r="F133" s="28"/>
+      <c r="G133" s="24"/>
       <c r="H133" s="12"/>
     </row>
-    <row r="134" spans="1:8" s="36" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A134" s="23"/>
-      <c r="B134" s="30"/>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A134" s="30"/>
+      <c r="B134" s="26"/>
       <c r="C134" s="13" t="s">
         <v>188</v>
       </c>
@@ -3604,13 +3590,13 @@
         <v>23</v>
       </c>
       <c r="E134" s="11"/>
-      <c r="F134" s="25"/>
-      <c r="G134" s="28"/>
+      <c r="F134" s="28"/>
+      <c r="G134" s="24"/>
       <c r="H134" s="12"/>
     </row>
-    <row r="135" spans="1:8" s="37" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A135" s="23"/>
-      <c r="B135" s="30"/>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A135" s="30"/>
+      <c r="B135" s="26"/>
       <c r="C135" s="13" t="s">
         <v>189</v>
       </c>
@@ -3618,13 +3604,13 @@
         <v>23</v>
       </c>
       <c r="E135" s="11"/>
-      <c r="F135" s="25"/>
-      <c r="G135" s="28"/>
+      <c r="F135" s="28"/>
+      <c r="G135" s="24"/>
       <c r="H135" s="12"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A136" s="23"/>
-      <c r="B136" s="30"/>
+      <c r="A136" s="30"/>
+      <c r="B136" s="26"/>
       <c r="C136" s="13" t="s">
         <v>190</v>
       </c>
@@ -3632,15 +3618,15 @@
         <v>1</v>
       </c>
       <c r="E136" s="12"/>
-      <c r="F136" s="26"/>
-      <c r="G136" s="29"/>
+      <c r="F136" s="29"/>
+      <c r="G136" s="25"/>
       <c r="H136" s="11"/>
     </row>
     <row r="137" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A137" s="23">
+      <c r="A137" s="30">
         <v>46169</v>
       </c>
-      <c r="B137" s="30" t="s">
+      <c r="B137" s="26" t="s">
         <v>170</v>
       </c>
       <c r="C137" s="13" t="s">
@@ -3650,17 +3636,17 @@
         <v>2</v>
       </c>
       <c r="E137" s="11"/>
-      <c r="F137" s="24" t="s">
+      <c r="F137" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G137" s="27">
+      <c r="G137" s="23">
         <v>6</v>
       </c>
       <c r="H137" s="11"/>
     </row>
-    <row r="138" spans="1:8" s="37" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A138" s="23"/>
-      <c r="B138" s="30"/>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A138" s="30"/>
+      <c r="B138" s="26"/>
       <c r="C138" s="13" t="s">
         <v>192</v>
       </c>
@@ -3668,13 +3654,13 @@
         <v>23</v>
       </c>
       <c r="E138" s="11"/>
-      <c r="F138" s="25"/>
-      <c r="G138" s="28"/>
+      <c r="F138" s="28"/>
+      <c r="G138" s="24"/>
       <c r="H138" s="11"/>
     </row>
-    <row r="139" spans="1:8" s="37" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A139" s="23"/>
-      <c r="B139" s="30"/>
+    <row r="139" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A139" s="30"/>
+      <c r="B139" s="26"/>
       <c r="C139" s="13" t="s">
         <v>193</v>
       </c>
@@ -3684,13 +3670,13 @@
       <c r="E139" s="12">
         <v>6</v>
       </c>
-      <c r="F139" s="25"/>
-      <c r="G139" s="28"/>
+      <c r="F139" s="28"/>
+      <c r="G139" s="24"/>
       <c r="H139" s="11"/>
     </row>
-    <row r="140" spans="1:8" s="37" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A140" s="23"/>
-      <c r="B140" s="30"/>
+    <row r="140" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A140" s="30"/>
+      <c r="B140" s="26"/>
       <c r="C140" s="13" t="s">
         <v>194</v>
       </c>
@@ -3698,13 +3684,13 @@
         <v>1</v>
       </c>
       <c r="E140" s="11"/>
-      <c r="F140" s="25"/>
-      <c r="G140" s="28"/>
+      <c r="F140" s="28"/>
+      <c r="G140" s="24"/>
       <c r="H140" s="11"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A141" s="23"/>
-      <c r="B141" s="30"/>
+      <c r="A141" s="30"/>
+      <c r="B141" s="26"/>
       <c r="C141" s="13" t="s">
         <v>195</v>
       </c>
@@ -3712,13 +3698,13 @@
         <v>1</v>
       </c>
       <c r="E141" s="11"/>
-      <c r="F141" s="25"/>
-      <c r="G141" s="28"/>
+      <c r="F141" s="28"/>
+      <c r="G141" s="24"/>
       <c r="H141" s="12"/>
     </row>
     <row r="142" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A142" s="23"/>
-      <c r="B142" s="30"/>
+      <c r="A142" s="30"/>
+      <c r="B142" s="26"/>
       <c r="C142" s="13" t="s">
         <v>196</v>
       </c>
@@ -3726,15 +3712,15 @@
         <v>1</v>
       </c>
       <c r="E142" s="12"/>
-      <c r="F142" s="26"/>
-      <c r="G142" s="29"/>
+      <c r="F142" s="29"/>
+      <c r="G142" s="25"/>
       <c r="H142" s="11"/>
     </row>
     <row r="143" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A143" s="23">
+      <c r="A143" s="30">
         <v>46170</v>
       </c>
-      <c r="B143" s="30" t="s">
+      <c r="B143" s="26" t="s">
         <v>171</v>
       </c>
       <c r="C143" s="13" t="s">
@@ -3744,17 +3730,17 @@
         <v>1</v>
       </c>
       <c r="E143" s="11"/>
-      <c r="F143" s="24" t="s">
+      <c r="F143" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G143" s="27">
+      <c r="G143" s="23">
         <v>6</v>
       </c>
       <c r="H143" s="11"/>
     </row>
-    <row r="144" spans="1:8" s="38" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A144" s="23"/>
-      <c r="B144" s="30"/>
+    <row r="144" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A144" s="30"/>
+      <c r="B144" s="26"/>
       <c r="C144" s="13" t="s">
         <v>198</v>
       </c>
@@ -3762,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="E144" s="11"/>
-      <c r="F144" s="25"/>
-      <c r="G144" s="28"/>
+      <c r="F144" s="28"/>
+      <c r="G144" s="24"/>
       <c r="H144" s="11"/>
     </row>
-    <row r="145" spans="1:8" s="38" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A145" s="23"/>
-      <c r="B145" s="30"/>
+    <row r="145" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A145" s="30"/>
+      <c r="B145" s="26"/>
       <c r="C145" s="13" t="s">
         <v>199</v>
       </c>
@@ -3776,13 +3762,13 @@
         <v>23</v>
       </c>
       <c r="E145" s="11"/>
-      <c r="F145" s="25"/>
-      <c r="G145" s="28"/>
+      <c r="F145" s="28"/>
+      <c r="G145" s="24"/>
       <c r="H145" s="11"/>
     </row>
-    <row r="146" spans="1:8" s="38" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A146" s="23"/>
-      <c r="B146" s="30"/>
+    <row r="146" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A146" s="30"/>
+      <c r="B146" s="26"/>
       <c r="C146" s="13" t="s">
         <v>200</v>
       </c>
@@ -3792,13 +3778,13 @@
       <c r="E146" s="12">
         <v>6</v>
       </c>
-      <c r="F146" s="25"/>
-      <c r="G146" s="28"/>
+      <c r="F146" s="28"/>
+      <c r="G146" s="24"/>
       <c r="H146" s="11"/>
     </row>
-    <row r="147" spans="1:8" s="38" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A147" s="23"/>
-      <c r="B147" s="30"/>
+    <row r="147" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A147" s="30"/>
+      <c r="B147" s="26"/>
       <c r="C147" s="13" t="s">
         <v>201</v>
       </c>
@@ -3806,13 +3792,13 @@
         <v>2</v>
       </c>
       <c r="E147" s="11"/>
-      <c r="F147" s="25"/>
-      <c r="G147" s="28"/>
+      <c r="F147" s="28"/>
+      <c r="G147" s="24"/>
       <c r="H147" s="11"/>
     </row>
-    <row r="148" spans="1:8" s="38" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A148" s="23"/>
-      <c r="B148" s="30"/>
+    <row r="148" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A148" s="30"/>
+      <c r="B148" s="26"/>
       <c r="C148" s="13" t="s">
         <v>202</v>
       </c>
@@ -3820,13 +3806,13 @@
         <v>23</v>
       </c>
       <c r="E148" s="11"/>
-      <c r="F148" s="25"/>
-      <c r="G148" s="28"/>
+      <c r="F148" s="28"/>
+      <c r="G148" s="24"/>
       <c r="H148" s="11"/>
     </row>
     <row r="149" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A149" s="23"/>
-      <c r="B149" s="30"/>
+      <c r="A149" s="30"/>
+      <c r="B149" s="26"/>
       <c r="C149" s="13" t="s">
         <v>203</v>
       </c>
@@ -3834,15 +3820,15 @@
         <v>23</v>
       </c>
       <c r="E149" s="12"/>
-      <c r="F149" s="26"/>
-      <c r="G149" s="29"/>
+      <c r="F149" s="29"/>
+      <c r="G149" s="25"/>
       <c r="H149" s="12"/>
     </row>
     <row r="150" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A150" s="23">
+      <c r="A150" s="30">
         <v>46171</v>
       </c>
-      <c r="B150" s="30" t="s">
+      <c r="B150" s="26" t="s">
         <v>172</v>
       </c>
       <c r="C150" s="13" t="s">
@@ -3852,17 +3838,17 @@
         <v>1</v>
       </c>
       <c r="E150" s="11"/>
-      <c r="F150" s="24" t="s">
+      <c r="F150" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G150" s="27">
+      <c r="G150" s="23">
         <v>6</v>
       </c>
       <c r="H150" s="11"/>
     </row>
-    <row r="151" spans="1:8" s="39" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A151" s="23"/>
-      <c r="B151" s="30"/>
+    <row r="151" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A151" s="30"/>
+      <c r="B151" s="26"/>
       <c r="C151" s="13" t="s">
         <v>205</v>
       </c>
@@ -3870,13 +3856,13 @@
         <v>1</v>
       </c>
       <c r="E151" s="11"/>
-      <c r="F151" s="25"/>
-      <c r="G151" s="28"/>
+      <c r="F151" s="28"/>
+      <c r="G151" s="24"/>
       <c r="H151" s="11"/>
     </row>
-    <row r="152" spans="1:8" s="39" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A152" s="23"/>
-      <c r="B152" s="30"/>
+    <row r="152" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A152" s="30"/>
+      <c r="B152" s="26"/>
       <c r="C152" s="13" t="s">
         <v>206</v>
       </c>
@@ -3886,13 +3872,13 @@
       <c r="E152" s="12">
         <v>6</v>
       </c>
-      <c r="F152" s="25"/>
-      <c r="G152" s="28"/>
+      <c r="F152" s="28"/>
+      <c r="G152" s="24"/>
       <c r="H152" s="11"/>
     </row>
-    <row r="153" spans="1:8" s="39" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A153" s="23"/>
-      <c r="B153" s="30"/>
+    <row r="153" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A153" s="30"/>
+      <c r="B153" s="26"/>
       <c r="C153" s="13" t="s">
         <v>207</v>
       </c>
@@ -3900,13 +3886,13 @@
         <v>23</v>
       </c>
       <c r="E153" s="11"/>
-      <c r="F153" s="25"/>
-      <c r="G153" s="28"/>
+      <c r="F153" s="28"/>
+      <c r="G153" s="24"/>
       <c r="H153" s="11"/>
     </row>
-    <row r="154" spans="1:8" s="39" customFormat="1" ht="99" x14ac:dyDescent="0.5">
-      <c r="A154" s="23"/>
-      <c r="B154" s="30"/>
+    <row r="154" spans="1:8" ht="99" x14ac:dyDescent="0.5">
+      <c r="A154" s="30"/>
+      <c r="B154" s="26"/>
       <c r="C154" s="13" t="s">
         <v>208</v>
       </c>
@@ -3914,13 +3900,13 @@
         <v>2</v>
       </c>
       <c r="E154" s="11"/>
-      <c r="F154" s="25"/>
-      <c r="G154" s="28"/>
+      <c r="F154" s="28"/>
+      <c r="G154" s="24"/>
       <c r="H154" s="11"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A155" s="23"/>
-      <c r="B155" s="30"/>
+      <c r="A155" s="30"/>
+      <c r="B155" s="26"/>
       <c r="C155" s="13" t="s">
         <v>209</v>
       </c>
@@ -3928,15 +3914,15 @@
         <v>1</v>
       </c>
       <c r="E155" s="12"/>
-      <c r="F155" s="26"/>
-      <c r="G155" s="29"/>
+      <c r="F155" s="29"/>
+      <c r="G155" s="25"/>
       <c r="H155" s="12"/>
     </row>
     <row r="156" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A156" s="23">
+      <c r="A156" s="30">
         <v>46174</v>
       </c>
-      <c r="B156" s="30" t="s">
+      <c r="B156" s="26" t="s">
         <v>173</v>
       </c>
       <c r="C156" s="13" t="s">
@@ -3946,17 +3932,17 @@
         <v>1</v>
       </c>
       <c r="E156" s="11"/>
-      <c r="F156" s="24" t="s">
+      <c r="F156" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G156" s="27">
+      <c r="G156" s="23">
         <v>6</v>
       </c>
       <c r="H156" s="11"/>
     </row>
-    <row r="157" spans="1:8" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A157" s="23"/>
-      <c r="B157" s="30"/>
+    <row r="157" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A157" s="30"/>
+      <c r="B157" s="26"/>
       <c r="C157" s="13" t="s">
         <v>211</v>
       </c>
@@ -3964,13 +3950,13 @@
         <v>23</v>
       </c>
       <c r="E157" s="11"/>
-      <c r="F157" s="25"/>
-      <c r="G157" s="28"/>
+      <c r="F157" s="28"/>
+      <c r="G157" s="24"/>
       <c r="H157" s="11"/>
     </row>
-    <row r="158" spans="1:8" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A158" s="23"/>
-      <c r="B158" s="30"/>
+    <row r="158" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A158" s="30"/>
+      <c r="B158" s="26"/>
       <c r="C158" s="13" t="s">
         <v>212</v>
       </c>
@@ -3978,13 +3964,13 @@
         <v>1</v>
       </c>
       <c r="E158" s="11"/>
-      <c r="F158" s="25"/>
-      <c r="G158" s="28"/>
+      <c r="F158" s="28"/>
+      <c r="G158" s="24"/>
       <c r="H158" s="11"/>
     </row>
-    <row r="159" spans="1:8" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A159" s="23"/>
-      <c r="B159" s="30"/>
+    <row r="159" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A159" s="30"/>
+      <c r="B159" s="26"/>
       <c r="C159" s="13" t="s">
         <v>213</v>
       </c>
@@ -3994,13 +3980,13 @@
       <c r="E159" s="12">
         <v>6</v>
       </c>
-      <c r="F159" s="25"/>
-      <c r="G159" s="28"/>
+      <c r="F159" s="28"/>
+      <c r="G159" s="24"/>
       <c r="H159" s="11"/>
     </row>
-    <row r="160" spans="1:8" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A160" s="23"/>
-      <c r="B160" s="30"/>
+    <row r="160" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A160" s="30"/>
+      <c r="B160" s="26"/>
       <c r="C160" s="13" t="s">
         <v>214</v>
       </c>
@@ -4008,13 +3994,13 @@
         <v>2</v>
       </c>
       <c r="E160" s="11"/>
-      <c r="F160" s="25"/>
-      <c r="G160" s="28"/>
+      <c r="F160" s="28"/>
+      <c r="G160" s="24"/>
       <c r="H160" s="11"/>
     </row>
-    <row r="161" spans="1:8" s="40" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A161" s="23"/>
-      <c r="B161" s="30"/>
+    <row r="161" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A161" s="30"/>
+      <c r="B161" s="26"/>
       <c r="C161" s="13" t="s">
         <v>215</v>
       </c>
@@ -4022,13 +4008,13 @@
         <v>23</v>
       </c>
       <c r="E161" s="11"/>
-      <c r="F161" s="25"/>
-      <c r="G161" s="28"/>
+      <c r="F161" s="28"/>
+      <c r="G161" s="24"/>
       <c r="H161" s="11"/>
     </row>
     <row r="162" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A162" s="23"/>
-      <c r="B162" s="30"/>
+      <c r="A162" s="30"/>
+      <c r="B162" s="26"/>
       <c r="C162" s="13" t="s">
         <v>216</v>
       </c>
@@ -4036,15 +4022,15 @@
         <v>23</v>
       </c>
       <c r="E162" s="12"/>
-      <c r="F162" s="26"/>
-      <c r="G162" s="29"/>
+      <c r="F162" s="29"/>
+      <c r="G162" s="25"/>
       <c r="H162" s="12"/>
     </row>
     <row r="163" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A163" s="23">
+      <c r="A163" s="30">
         <v>46175</v>
       </c>
-      <c r="B163" s="35" t="s">
+      <c r="B163" s="31" t="s">
         <v>174</v>
       </c>
       <c r="C163" s="13" t="s">
@@ -4054,17 +4040,17 @@
         <v>1</v>
       </c>
       <c r="E163" s="11"/>
-      <c r="F163" s="24" t="s">
+      <c r="F163" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G163" s="27">
+      <c r="G163" s="23">
         <v>6</v>
       </c>
       <c r="H163" s="11"/>
     </row>
-    <row r="164" spans="1:8" s="41" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A164" s="23"/>
-      <c r="B164" s="35"/>
+    <row r="164" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A164" s="30"/>
+      <c r="B164" s="31"/>
       <c r="C164" s="13" t="s">
         <v>218</v>
       </c>
@@ -4072,13 +4058,13 @@
         <v>1</v>
       </c>
       <c r="E164" s="11"/>
-      <c r="F164" s="25"/>
-      <c r="G164" s="28"/>
+      <c r="F164" s="28"/>
+      <c r="G164" s="24"/>
       <c r="H164" s="11"/>
     </row>
-    <row r="165" spans="1:8" s="41" customFormat="1" ht="49.5" x14ac:dyDescent="0.5">
-      <c r="A165" s="23"/>
-      <c r="B165" s="35"/>
+    <row r="165" spans="1:8" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="A165" s="30"/>
+      <c r="B165" s="31"/>
       <c r="C165" s="13" t="s">
         <v>219</v>
       </c>
@@ -4088,13 +4074,13 @@
       <c r="E165" s="12">
         <v>6</v>
       </c>
-      <c r="F165" s="25"/>
-      <c r="G165" s="28"/>
+      <c r="F165" s="28"/>
+      <c r="G165" s="24"/>
       <c r="H165" s="11"/>
     </row>
-    <row r="166" spans="1:8" s="41" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A166" s="23"/>
-      <c r="B166" s="35"/>
+    <row r="166" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A166" s="30"/>
+      <c r="B166" s="31"/>
       <c r="C166" s="13" t="s">
         <v>220</v>
       </c>
@@ -4102,13 +4088,13 @@
         <v>2</v>
       </c>
       <c r="E166" s="11"/>
-      <c r="F166" s="25"/>
-      <c r="G166" s="28"/>
+      <c r="F166" s="28"/>
+      <c r="G166" s="24"/>
       <c r="H166" s="11"/>
     </row>
     <row r="167" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A167" s="23"/>
-      <c r="B167" s="35"/>
+      <c r="A167" s="30"/>
+      <c r="B167" s="31"/>
       <c r="C167" s="13" t="s">
         <v>221</v>
       </c>
@@ -4116,13 +4102,13 @@
         <v>23</v>
       </c>
       <c r="E167" s="11"/>
-      <c r="F167" s="25"/>
-      <c r="G167" s="28"/>
+      <c r="F167" s="28"/>
+      <c r="G167" s="24"/>
       <c r="H167" s="11"/>
     </row>
     <row r="168" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A168" s="23"/>
-      <c r="B168" s="35"/>
+      <c r="A168" s="30"/>
+      <c r="B168" s="31"/>
       <c r="C168" s="13" t="s">
         <v>222</v>
       </c>
@@ -4130,15 +4116,15 @@
         <v>23</v>
       </c>
       <c r="E168" s="12"/>
-      <c r="F168" s="26"/>
-      <c r="G168" s="29"/>
+      <c r="F168" s="29"/>
+      <c r="G168" s="25"/>
       <c r="H168" s="12"/>
     </row>
     <row r="169" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A169" s="23">
+      <c r="A169" s="30">
         <v>46176</v>
       </c>
-      <c r="B169" s="30" t="s">
+      <c r="B169" s="26" t="s">
         <v>175</v>
       </c>
       <c r="C169" s="13" t="s">
@@ -4148,17 +4134,17 @@
         <v>1</v>
       </c>
       <c r="E169" s="11"/>
-      <c r="F169" s="24" t="s">
+      <c r="F169" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G169" s="27">
+      <c r="G169" s="23">
         <v>6</v>
       </c>
       <c r="H169" s="11"/>
     </row>
-    <row r="170" spans="1:8" s="42" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A170" s="23"/>
-      <c r="B170" s="30"/>
+    <row r="170" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A170" s="30"/>
+      <c r="B170" s="26"/>
       <c r="C170" s="13" t="s">
         <v>224</v>
       </c>
@@ -4166,13 +4152,13 @@
         <v>22</v>
       </c>
       <c r="E170" s="11"/>
-      <c r="F170" s="25"/>
-      <c r="G170" s="28"/>
+      <c r="F170" s="28"/>
+      <c r="G170" s="24"/>
       <c r="H170" s="11"/>
     </row>
-    <row r="171" spans="1:8" s="42" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A171" s="23"/>
-      <c r="B171" s="30"/>
+    <row r="171" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A171" s="30"/>
+      <c r="B171" s="26"/>
       <c r="C171" s="13" t="s">
         <v>225</v>
       </c>
@@ -4182,13 +4168,13 @@
       <c r="E171" s="12">
         <v>6</v>
       </c>
-      <c r="F171" s="25"/>
-      <c r="G171" s="28"/>
+      <c r="F171" s="28"/>
+      <c r="G171" s="24"/>
       <c r="H171" s="11"/>
     </row>
-    <row r="172" spans="1:8" s="42" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A172" s="23"/>
-      <c r="B172" s="30"/>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A172" s="30"/>
+      <c r="B172" s="26"/>
       <c r="C172" s="13" t="s">
         <v>226</v>
       </c>
@@ -4196,13 +4182,13 @@
         <v>1</v>
       </c>
       <c r="E172" s="11"/>
-      <c r="F172" s="25"/>
-      <c r="G172" s="28"/>
+      <c r="F172" s="28"/>
+      <c r="G172" s="24"/>
       <c r="H172" s="11"/>
     </row>
-    <row r="173" spans="1:8" s="42" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A173" s="23"/>
-      <c r="B173" s="30"/>
+    <row r="173" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A173" s="30"/>
+      <c r="B173" s="26"/>
       <c r="C173" s="13" t="s">
         <v>227</v>
       </c>
@@ -4210,13 +4196,13 @@
         <v>1</v>
       </c>
       <c r="E173" s="11"/>
-      <c r="F173" s="25"/>
-      <c r="G173" s="28"/>
+      <c r="F173" s="28"/>
+      <c r="G173" s="24"/>
       <c r="H173" s="11"/>
     </row>
     <row r="174" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A174" s="23"/>
-      <c r="B174" s="30"/>
+      <c r="A174" s="30"/>
+      <c r="B174" s="26"/>
       <c r="C174" s="13" t="s">
         <v>228</v>
       </c>
@@ -4224,15 +4210,15 @@
         <v>1</v>
       </c>
       <c r="E174" s="12"/>
-      <c r="F174" s="26"/>
-      <c r="G174" s="29"/>
+      <c r="F174" s="29"/>
+      <c r="G174" s="25"/>
       <c r="H174" s="12"/>
     </row>
     <row r="175" spans="1:8" ht="82.5" x14ac:dyDescent="0.5">
-      <c r="A175" s="23">
+      <c r="A175" s="30">
         <v>46177</v>
       </c>
-      <c r="B175" s="30" t="s">
+      <c r="B175" s="26" t="s">
         <v>176</v>
       </c>
       <c r="C175" s="13" t="s">
@@ -4242,17 +4228,17 @@
         <v>22</v>
       </c>
       <c r="E175" s="11"/>
-      <c r="F175" s="24" t="s">
+      <c r="F175" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G175" s="27">
+      <c r="G175" s="23">
         <v>6</v>
       </c>
       <c r="H175" s="11"/>
     </row>
-    <row r="176" spans="1:8" s="43" customFormat="1" ht="82.5" x14ac:dyDescent="0.5">
-      <c r="A176" s="23"/>
-      <c r="B176" s="30"/>
+    <row r="176" spans="1:8" ht="82.5" x14ac:dyDescent="0.5">
+      <c r="A176" s="30"/>
+      <c r="B176" s="26"/>
       <c r="C176" s="13" t="s">
         <v>230</v>
       </c>
@@ -4262,13 +4248,13 @@
       <c r="E176" s="12">
         <v>6</v>
       </c>
-      <c r="F176" s="25"/>
-      <c r="G176" s="28"/>
+      <c r="F176" s="28"/>
+      <c r="G176" s="24"/>
       <c r="H176" s="11"/>
     </row>
-    <row r="177" spans="1:8" s="43" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A177" s="23"/>
-      <c r="B177" s="30"/>
+    <row r="177" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A177" s="30"/>
+      <c r="B177" s="26"/>
       <c r="C177" s="13" t="s">
         <v>233</v>
       </c>
@@ -4276,13 +4262,13 @@
         <v>1</v>
       </c>
       <c r="E177" s="11"/>
-      <c r="F177" s="25"/>
-      <c r="G177" s="28"/>
+      <c r="F177" s="28"/>
+      <c r="G177" s="24"/>
       <c r="H177" s="11"/>
     </row>
-    <row r="178" spans="1:8" s="43" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A178" s="23"/>
-      <c r="B178" s="30"/>
+    <row r="178" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A178" s="30"/>
+      <c r="B178" s="26"/>
       <c r="C178" s="13" t="s">
         <v>231</v>
       </c>
@@ -4290,13 +4276,13 @@
         <v>22</v>
       </c>
       <c r="E178" s="11"/>
-      <c r="F178" s="25"/>
-      <c r="G178" s="28"/>
+      <c r="F178" s="28"/>
+      <c r="G178" s="24"/>
       <c r="H178" s="11"/>
     </row>
     <row r="179" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A179" s="23"/>
-      <c r="B179" s="30"/>
+      <c r="A179" s="30"/>
+      <c r="B179" s="26"/>
       <c r="C179" s="13" t="s">
         <v>232</v>
       </c>
@@ -4304,15 +4290,15 @@
         <v>23</v>
       </c>
       <c r="E179" s="12"/>
-      <c r="F179" s="26"/>
-      <c r="G179" s="29"/>
+      <c r="F179" s="29"/>
+      <c r="G179" s="25"/>
       <c r="H179" s="11"/>
     </row>
     <row r="180" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A180" s="23">
+      <c r="A180" s="30">
         <v>46178</v>
       </c>
-      <c r="B180" s="30" t="s">
+      <c r="B180" s="26" t="s">
         <v>177</v>
       </c>
       <c r="C180" s="13" t="s">
@@ -4322,17 +4308,17 @@
         <v>1</v>
       </c>
       <c r="E180" s="11"/>
-      <c r="F180" s="24" t="s">
+      <c r="F180" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G180" s="27">
+      <c r="G180" s="23">
         <v>6</v>
       </c>
       <c r="H180" s="12"/>
     </row>
-    <row r="181" spans="1:8" s="44" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A181" s="23"/>
-      <c r="B181" s="30"/>
+    <row r="181" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A181" s="30"/>
+      <c r="B181" s="26"/>
       <c r="C181" s="13" t="s">
         <v>235</v>
       </c>
@@ -4340,13 +4326,13 @@
         <v>23</v>
       </c>
       <c r="E181" s="11"/>
-      <c r="F181" s="25"/>
-      <c r="G181" s="28"/>
+      <c r="F181" s="28"/>
+      <c r="G181" s="24"/>
       <c r="H181" s="12"/>
     </row>
-    <row r="182" spans="1:8" s="44" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A182" s="23"/>
-      <c r="B182" s="30"/>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A182" s="30"/>
+      <c r="B182" s="26"/>
       <c r="C182" s="13" t="s">
         <v>236</v>
       </c>
@@ -4356,13 +4342,13 @@
       <c r="E182" s="12">
         <v>6</v>
       </c>
-      <c r="F182" s="25"/>
-      <c r="G182" s="28"/>
+      <c r="F182" s="28"/>
+      <c r="G182" s="24"/>
       <c r="H182" s="12"/>
     </row>
-    <row r="183" spans="1:8" s="44" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A183" s="23"/>
-      <c r="B183" s="30"/>
+    <row r="183" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A183" s="30"/>
+      <c r="B183" s="26"/>
       <c r="C183" s="13" t="s">
         <v>237</v>
       </c>
@@ -4370,13 +4356,13 @@
         <v>1</v>
       </c>
       <c r="E183" s="11"/>
-      <c r="F183" s="25"/>
-      <c r="G183" s="28"/>
+      <c r="F183" s="28"/>
+      <c r="G183" s="24"/>
       <c r="H183" s="12"/>
     </row>
-    <row r="184" spans="1:8" s="44" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A184" s="23"/>
-      <c r="B184" s="30"/>
+    <row r="184" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A184" s="30"/>
+      <c r="B184" s="26"/>
       <c r="C184" s="13" t="s">
         <v>238</v>
       </c>
@@ -4384,13 +4370,13 @@
         <v>2</v>
       </c>
       <c r="E184" s="11"/>
-      <c r="F184" s="25"/>
-      <c r="G184" s="28"/>
+      <c r="F184" s="28"/>
+      <c r="G184" s="24"/>
       <c r="H184" s="12"/>
     </row>
     <row r="185" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A185" s="23"/>
-      <c r="B185" s="30"/>
+      <c r="A185" s="30"/>
+      <c r="B185" s="26"/>
       <c r="C185" s="13" t="s">
         <v>239</v>
       </c>
@@ -4398,15 +4384,15 @@
         <v>1</v>
       </c>
       <c r="E185" s="12"/>
-      <c r="F185" s="26"/>
-      <c r="G185" s="29"/>
+      <c r="F185" s="29"/>
+      <c r="G185" s="25"/>
       <c r="H185" s="11"/>
     </row>
     <row r="186" spans="1:8" ht="116" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A186" s="23">
+      <c r="A186" s="30">
         <v>46181</v>
       </c>
-      <c r="B186" s="30" t="s">
+      <c r="B186" s="26" t="s">
         <v>178</v>
       </c>
       <c r="C186" s="13" t="s">
@@ -4416,17 +4402,17 @@
         <v>1</v>
       </c>
       <c r="E186" s="11"/>
-      <c r="F186" s="24" t="s">
+      <c r="F186" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G186" s="27">
+      <c r="G186" s="23">
         <v>6</v>
       </c>
       <c r="H186" s="11"/>
     </row>
-    <row r="187" spans="1:8" s="45" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A187" s="23"/>
-      <c r="B187" s="30"/>
+    <row r="187" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A187" s="30"/>
+      <c r="B187" s="26"/>
       <c r="C187" s="13" t="s">
         <v>241</v>
       </c>
@@ -4434,13 +4420,13 @@
         <v>22</v>
       </c>
       <c r="E187" s="11"/>
-      <c r="F187" s="25"/>
-      <c r="G187" s="28"/>
+      <c r="F187" s="28"/>
+      <c r="G187" s="24"/>
       <c r="H187" s="11"/>
     </row>
-    <row r="188" spans="1:8" s="45" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A188" s="23"/>
-      <c r="B188" s="30"/>
+    <row r="188" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A188" s="30"/>
+      <c r="B188" s="26"/>
       <c r="C188" s="13" t="s">
         <v>242</v>
       </c>
@@ -4450,13 +4436,13 @@
       <c r="E188" s="12">
         <v>6</v>
       </c>
-      <c r="F188" s="25"/>
-      <c r="G188" s="28"/>
+      <c r="F188" s="28"/>
+      <c r="G188" s="24"/>
       <c r="H188" s="11"/>
     </row>
-    <row r="189" spans="1:8" s="45" customFormat="1" ht="82.5" x14ac:dyDescent="0.5">
-      <c r="A189" s="23"/>
-      <c r="B189" s="30"/>
+    <row r="189" spans="1:8" ht="82.5" x14ac:dyDescent="0.5">
+      <c r="A189" s="30"/>
+      <c r="B189" s="26"/>
       <c r="C189" s="13" t="s">
         <v>243</v>
       </c>
@@ -4464,13 +4450,13 @@
         <v>2</v>
       </c>
       <c r="E189" s="11"/>
-      <c r="F189" s="25"/>
-      <c r="G189" s="28"/>
+      <c r="F189" s="28"/>
+      <c r="G189" s="24"/>
       <c r="H189" s="11"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A190" s="23"/>
-      <c r="B190" s="30"/>
+      <c r="A190" s="30"/>
+      <c r="B190" s="26"/>
       <c r="C190" s="13" t="s">
         <v>244</v>
       </c>
@@ -4478,15 +4464,15 @@
         <v>1</v>
       </c>
       <c r="E190" s="12"/>
-      <c r="F190" s="26"/>
-      <c r="G190" s="29"/>
+      <c r="F190" s="29"/>
+      <c r="G190" s="25"/>
       <c r="H190" s="12"/>
     </row>
     <row r="191" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A191" s="23">
+      <c r="A191" s="30">
         <v>46182</v>
       </c>
-      <c r="B191" s="30" t="s">
+      <c r="B191" s="26" t="s">
         <v>179</v>
       </c>
       <c r="C191" s="13" t="s">
@@ -4496,17 +4482,17 @@
         <v>1</v>
       </c>
       <c r="E191" s="11"/>
-      <c r="F191" s="24" t="s">
+      <c r="F191" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G191" s="27">
+      <c r="G191" s="23">
         <v>6</v>
       </c>
       <c r="H191" s="11"/>
     </row>
-    <row r="192" spans="1:8" s="46" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A192" s="23"/>
-      <c r="B192" s="30"/>
+    <row r="192" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A192" s="30"/>
+      <c r="B192" s="26"/>
       <c r="C192" s="13" t="s">
         <v>246</v>
       </c>
@@ -4514,13 +4500,13 @@
         <v>1</v>
       </c>
       <c r="E192" s="11"/>
-      <c r="F192" s="25"/>
-      <c r="G192" s="28"/>
+      <c r="F192" s="28"/>
+      <c r="G192" s="24"/>
       <c r="H192" s="11"/>
     </row>
-    <row r="193" spans="1:8" s="46" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A193" s="23"/>
-      <c r="B193" s="30"/>
+    <row r="193" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A193" s="30"/>
+      <c r="B193" s="26"/>
       <c r="C193" s="13" t="s">
         <v>247</v>
       </c>
@@ -4528,13 +4514,13 @@
         <v>1</v>
       </c>
       <c r="E193" s="11"/>
-      <c r="F193" s="25"/>
-      <c r="G193" s="28"/>
+      <c r="F193" s="28"/>
+      <c r="G193" s="24"/>
       <c r="H193" s="11"/>
     </row>
-    <row r="194" spans="1:8" s="46" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A194" s="23"/>
-      <c r="B194" s="30"/>
+    <row r="194" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A194" s="30"/>
+      <c r="B194" s="26"/>
       <c r="C194" s="13" t="s">
         <v>248</v>
       </c>
@@ -4544,13 +4530,13 @@
       <c r="E194" s="12">
         <v>6</v>
       </c>
-      <c r="F194" s="25"/>
-      <c r="G194" s="28"/>
+      <c r="F194" s="28"/>
+      <c r="G194" s="24"/>
       <c r="H194" s="11"/>
     </row>
-    <row r="195" spans="1:8" s="46" customFormat="1" ht="49.5" x14ac:dyDescent="0.5">
-      <c r="A195" s="23"/>
-      <c r="B195" s="30"/>
+    <row r="195" spans="1:8" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="A195" s="30"/>
+      <c r="B195" s="26"/>
       <c r="C195" s="13" t="s">
         <v>249</v>
       </c>
@@ -4558,13 +4544,13 @@
         <v>1</v>
       </c>
       <c r="E195" s="11"/>
-      <c r="F195" s="25"/>
-      <c r="G195" s="28"/>
+      <c r="F195" s="28"/>
+      <c r="G195" s="24"/>
       <c r="H195" s="11"/>
     </row>
-    <row r="196" spans="1:8" s="46" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A196" s="23"/>
-      <c r="B196" s="30"/>
+    <row r="196" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A196" s="30"/>
+      <c r="B196" s="26"/>
       <c r="C196" s="13" t="s">
         <v>250</v>
       </c>
@@ -4572,13 +4558,13 @@
         <v>1</v>
       </c>
       <c r="E196" s="11"/>
-      <c r="F196" s="25"/>
-      <c r="G196" s="28"/>
+      <c r="F196" s="28"/>
+      <c r="G196" s="24"/>
       <c r="H196" s="11"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A197" s="23"/>
-      <c r="B197" s="30"/>
+      <c r="A197" s="30"/>
+      <c r="B197" s="26"/>
       <c r="C197" s="13" t="s">
         <v>251</v>
       </c>
@@ -4586,15 +4572,15 @@
         <v>23</v>
       </c>
       <c r="E197" s="12"/>
-      <c r="F197" s="26"/>
-      <c r="G197" s="29"/>
+      <c r="F197" s="29"/>
+      <c r="G197" s="25"/>
       <c r="H197" s="12"/>
     </row>
     <row r="198" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A198" s="23">
+      <c r="A198" s="30">
         <v>46183</v>
       </c>
-      <c r="B198" s="30" t="s">
+      <c r="B198" s="26" t="s">
         <v>180</v>
       </c>
       <c r="C198" s="13" t="s">
@@ -4604,17 +4590,17 @@
         <v>1</v>
       </c>
       <c r="E198" s="11"/>
-      <c r="F198" s="24" t="s">
+      <c r="F198" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G198" s="27">
+      <c r="G198" s="23">
         <v>6</v>
       </c>
       <c r="H198" s="11"/>
     </row>
-    <row r="199" spans="1:8" s="47" customFormat="1" ht="49.5" x14ac:dyDescent="0.5">
-      <c r="A199" s="23"/>
-      <c r="B199" s="30"/>
+    <row r="199" spans="1:8" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="A199" s="30"/>
+      <c r="B199" s="26"/>
       <c r="C199" s="13" t="s">
         <v>253</v>
       </c>
@@ -4622,13 +4608,13 @@
         <v>1</v>
       </c>
       <c r="E199" s="11"/>
-      <c r="F199" s="25"/>
-      <c r="G199" s="28"/>
+      <c r="F199" s="28"/>
+      <c r="G199" s="24"/>
       <c r="H199" s="11"/>
     </row>
-    <row r="200" spans="1:8" s="47" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A200" s="23"/>
-      <c r="B200" s="30"/>
+    <row r="200" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A200" s="30"/>
+      <c r="B200" s="26"/>
       <c r="C200" s="13" t="s">
         <v>254</v>
       </c>
@@ -4638,13 +4624,13 @@
       <c r="E200" s="12">
         <v>6</v>
       </c>
-      <c r="F200" s="25"/>
-      <c r="G200" s="28"/>
+      <c r="F200" s="28"/>
+      <c r="G200" s="24"/>
       <c r="H200" s="11"/>
     </row>
-    <row r="201" spans="1:8" s="47" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A201" s="23"/>
-      <c r="B201" s="30"/>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A201" s="30"/>
+      <c r="B201" s="26"/>
       <c r="C201" s="13" t="s">
         <v>255</v>
       </c>
@@ -4652,13 +4638,13 @@
         <v>23</v>
       </c>
       <c r="E201" s="11"/>
-      <c r="F201" s="25"/>
-      <c r="G201" s="28"/>
+      <c r="F201" s="28"/>
+      <c r="G201" s="24"/>
       <c r="H201" s="11"/>
     </row>
-    <row r="202" spans="1:8" s="47" customFormat="1" ht="49.5" x14ac:dyDescent="0.5">
-      <c r="A202" s="23"/>
-      <c r="B202" s="30"/>
+    <row r="202" spans="1:8" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="A202" s="30"/>
+      <c r="B202" s="26"/>
       <c r="C202" s="13" t="s">
         <v>256</v>
       </c>
@@ -4666,13 +4652,13 @@
         <v>2</v>
       </c>
       <c r="E202" s="11"/>
-      <c r="F202" s="25"/>
-      <c r="G202" s="28"/>
+      <c r="F202" s="28"/>
+      <c r="G202" s="24"/>
       <c r="H202" s="11"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A203" s="23"/>
-      <c r="B203" s="30"/>
+      <c r="A203" s="30"/>
+      <c r="B203" s="26"/>
       <c r="C203" s="13" t="s">
         <v>257</v>
       </c>
@@ -4680,15 +4666,15 @@
         <v>1</v>
       </c>
       <c r="E203" s="12"/>
-      <c r="F203" s="26"/>
-      <c r="G203" s="29"/>
+      <c r="F203" s="29"/>
+      <c r="G203" s="25"/>
       <c r="H203" s="12"/>
     </row>
     <row r="204" spans="1:8" ht="66" x14ac:dyDescent="0.5">
-      <c r="A204" s="23">
+      <c r="A204" s="30">
         <v>46184</v>
       </c>
-      <c r="B204" s="30" t="s">
+      <c r="B204" s="26" t="s">
         <v>181</v>
       </c>
       <c r="C204" s="13" t="s">
@@ -4698,17 +4684,17 @@
         <v>2</v>
       </c>
       <c r="E204" s="11"/>
-      <c r="F204" s="24" t="s">
+      <c r="F204" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G204" s="27">
+      <c r="G204" s="23">
         <v>6</v>
       </c>
       <c r="H204" s="11"/>
     </row>
-    <row r="205" spans="1:8" s="48" customFormat="1" ht="33" x14ac:dyDescent="0.5">
-      <c r="A205" s="23"/>
-      <c r="B205" s="30"/>
+    <row r="205" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A205" s="30"/>
+      <c r="B205" s="26"/>
       <c r="C205" s="13" t="s">
         <v>258</v>
       </c>
@@ -4718,13 +4704,13 @@
       <c r="E205" s="12">
         <v>6</v>
       </c>
-      <c r="F205" s="25"/>
-      <c r="G205" s="28"/>
+      <c r="F205" s="28"/>
+      <c r="G205" s="24"/>
       <c r="H205" s="11"/>
     </row>
     <row r="206" spans="1:8" ht="82.5" x14ac:dyDescent="0.5">
-      <c r="A206" s="23"/>
-      <c r="B206" s="30"/>
+      <c r="A206" s="30"/>
+      <c r="B206" s="26"/>
       <c r="C206" s="13" t="s">
         <v>260</v>
       </c>
@@ -4732,15 +4718,15 @@
         <v>3</v>
       </c>
       <c r="E206" s="12"/>
-      <c r="F206" s="26"/>
-      <c r="G206" s="29"/>
+      <c r="F206" s="29"/>
+      <c r="G206" s="25"/>
       <c r="H206" s="11"/>
     </row>
     <row r="207" spans="1:8" ht="66" x14ac:dyDescent="0.5">
-      <c r="A207" s="23">
+      <c r="A207" s="30">
         <v>46185</v>
       </c>
-      <c r="B207" s="30" t="s">
+      <c r="B207" s="26" t="s">
         <v>182</v>
       </c>
       <c r="C207" s="13" t="s">
@@ -4750,17 +4736,17 @@
         <v>22</v>
       </c>
       <c r="E207" s="11"/>
-      <c r="F207" s="24" t="s">
+      <c r="F207" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G207" s="27">
+      <c r="G207" s="23">
         <v>6</v>
       </c>
       <c r="H207" s="12"/>
     </row>
-    <row r="208" spans="1:8" s="49" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A208" s="23"/>
-      <c r="B208" s="30"/>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A208" s="30"/>
+      <c r="B208" s="26"/>
       <c r="C208" s="13" t="s">
         <v>112</v>
       </c>
@@ -4768,13 +4754,13 @@
         <v>1</v>
       </c>
       <c r="E208" s="11"/>
-      <c r="F208" s="25"/>
-      <c r="G208" s="28"/>
+      <c r="F208" s="28"/>
+      <c r="G208" s="24"/>
       <c r="H208" s="12"/>
     </row>
-    <row r="209" spans="1:8" s="49" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A209" s="23"/>
-      <c r="B209" s="30"/>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A209" s="30"/>
+      <c r="B209" s="26"/>
       <c r="C209" s="13" t="s">
         <v>262</v>
       </c>
@@ -4782,13 +4768,13 @@
         <v>23</v>
       </c>
       <c r="E209" s="11"/>
-      <c r="F209" s="25"/>
-      <c r="G209" s="28"/>
+      <c r="F209" s="28"/>
+      <c r="G209" s="24"/>
       <c r="H209" s="12"/>
     </row>
-    <row r="210" spans="1:8" s="49" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A210" s="23"/>
-      <c r="B210" s="30"/>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A210" s="30"/>
+      <c r="B210" s="26"/>
       <c r="C210" s="13" t="s">
         <v>263</v>
       </c>
@@ -4798,13 +4784,13 @@
       <c r="E210" s="12">
         <v>6</v>
       </c>
-      <c r="F210" s="25"/>
-      <c r="G210" s="28"/>
+      <c r="F210" s="28"/>
+      <c r="G210" s="24"/>
       <c r="H210" s="12"/>
     </row>
-    <row r="211" spans="1:8" s="49" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A211" s="23"/>
-      <c r="B211" s="30"/>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A211" s="30"/>
+      <c r="B211" s="26"/>
       <c r="C211" s="13" t="s">
         <v>264</v>
       </c>
@@ -4812,13 +4798,13 @@
         <v>1</v>
       </c>
       <c r="E211" s="11"/>
-      <c r="F211" s="25"/>
-      <c r="G211" s="28"/>
+      <c r="F211" s="28"/>
+      <c r="G211" s="24"/>
       <c r="H211" s="12"/>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A212" s="23"/>
-      <c r="B212" s="30"/>
+      <c r="A212" s="30"/>
+      <c r="B212" s="26"/>
       <c r="C212" s="13" t="s">
         <v>265</v>
       </c>
@@ -4826,8 +4812,8 @@
         <v>1</v>
       </c>
       <c r="E212" s="12"/>
-      <c r="F212" s="26"/>
-      <c r="G212" s="29"/>
+      <c r="F212" s="29"/>
+      <c r="G212" s="25"/>
       <c r="H212" s="11"/>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.5">
@@ -4964,18 +4950,139 @@
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="G204:G206"/>
-    <mergeCell ref="B207:B212"/>
-    <mergeCell ref="F207:F212"/>
-    <mergeCell ref="G207:G212"/>
-    <mergeCell ref="B204:B206"/>
-    <mergeCell ref="F204:F206"/>
-    <mergeCell ref="A198:A203"/>
-    <mergeCell ref="A204:A206"/>
-    <mergeCell ref="A207:A212"/>
-    <mergeCell ref="B198:B203"/>
-    <mergeCell ref="F198:F203"/>
-    <mergeCell ref="G198:G203"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="B88:B93"/>
+    <mergeCell ref="F88:F93"/>
+    <mergeCell ref="G88:G93"/>
+    <mergeCell ref="A104:A109"/>
+    <mergeCell ref="B104:B109"/>
+    <mergeCell ref="F104:F109"/>
+    <mergeCell ref="G104:G109"/>
+    <mergeCell ref="A65:A71"/>
+    <mergeCell ref="B65:B71"/>
+    <mergeCell ref="F65:F71"/>
+    <mergeCell ref="G65:G71"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="G94:G97"/>
+    <mergeCell ref="A98:A103"/>
+    <mergeCell ref="B98:B103"/>
+    <mergeCell ref="F98:F103"/>
+    <mergeCell ref="G48:G53"/>
+    <mergeCell ref="A83:A87"/>
+    <mergeCell ref="B83:B87"/>
+    <mergeCell ref="F83:F87"/>
+    <mergeCell ref="G83:G87"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="F54:F58"/>
+    <mergeCell ref="G54:G58"/>
+    <mergeCell ref="A59:A64"/>
+    <mergeCell ref="B59:B64"/>
+    <mergeCell ref="F59:F64"/>
+    <mergeCell ref="G59:G64"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="F72:F76"/>
+    <mergeCell ref="G72:G76"/>
+    <mergeCell ref="A77:A82"/>
+    <mergeCell ref="B77:B82"/>
+    <mergeCell ref="F77:F82"/>
+    <mergeCell ref="G77:G82"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="A150:A155"/>
+    <mergeCell ref="B150:B155"/>
+    <mergeCell ref="F150:F155"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="F45:F47"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="A143:A149"/>
+    <mergeCell ref="F143:F149"/>
+    <mergeCell ref="G143:G149"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A123:A128"/>
+    <mergeCell ref="B123:B128"/>
+    <mergeCell ref="F123:F128"/>
+    <mergeCell ref="G123:G128"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="G98:G103"/>
+    <mergeCell ref="A156:A162"/>
+    <mergeCell ref="F156:F162"/>
+    <mergeCell ref="G156:G162"/>
+    <mergeCell ref="B156:B162"/>
+    <mergeCell ref="G150:G155"/>
+    <mergeCell ref="A129:A136"/>
+    <mergeCell ref="B129:B136"/>
+    <mergeCell ref="F129:F136"/>
+    <mergeCell ref="G129:G136"/>
+    <mergeCell ref="A137:A142"/>
+    <mergeCell ref="B137:B142"/>
+    <mergeCell ref="F137:F142"/>
+    <mergeCell ref="G137:G142"/>
+    <mergeCell ref="B143:B149"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="G110:G113"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="G114:G117"/>
+    <mergeCell ref="A118:A122"/>
+    <mergeCell ref="B118:B122"/>
+    <mergeCell ref="F118:F122"/>
+    <mergeCell ref="G118:G122"/>
     <mergeCell ref="A169:A174"/>
     <mergeCell ref="A175:A179"/>
     <mergeCell ref="A180:A185"/>
@@ -5000,139 +5107,18 @@
     <mergeCell ref="F169:F174"/>
     <mergeCell ref="B186:B190"/>
     <mergeCell ref="F186:F190"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="G110:G113"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="G114:G117"/>
-    <mergeCell ref="A118:A122"/>
-    <mergeCell ref="B118:B122"/>
-    <mergeCell ref="F118:F122"/>
-    <mergeCell ref="G118:G122"/>
-    <mergeCell ref="A123:A128"/>
-    <mergeCell ref="B123:B128"/>
-    <mergeCell ref="F123:F128"/>
-    <mergeCell ref="G123:G128"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="G98:G103"/>
-    <mergeCell ref="A156:A162"/>
-    <mergeCell ref="F156:F162"/>
-    <mergeCell ref="G156:G162"/>
-    <mergeCell ref="B156:B162"/>
-    <mergeCell ref="G150:G155"/>
-    <mergeCell ref="A129:A136"/>
-    <mergeCell ref="B129:B136"/>
-    <mergeCell ref="F129:F136"/>
-    <mergeCell ref="G129:G136"/>
-    <mergeCell ref="A137:A142"/>
-    <mergeCell ref="B137:B142"/>
-    <mergeCell ref="F137:F142"/>
-    <mergeCell ref="G137:G142"/>
-    <mergeCell ref="B143:B149"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="F45:F47"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="A143:A149"/>
-    <mergeCell ref="F143:F149"/>
-    <mergeCell ref="G143:G149"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A150:A155"/>
-    <mergeCell ref="B150:B155"/>
-    <mergeCell ref="F150:F155"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="F33:F35"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="G48:G53"/>
-    <mergeCell ref="A83:A87"/>
-    <mergeCell ref="B83:B87"/>
-    <mergeCell ref="F83:F87"/>
-    <mergeCell ref="G83:G87"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="F54:F58"/>
-    <mergeCell ref="G54:G58"/>
-    <mergeCell ref="A59:A64"/>
-    <mergeCell ref="B59:B64"/>
-    <mergeCell ref="F59:F64"/>
-    <mergeCell ref="G59:G64"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="F72:F76"/>
-    <mergeCell ref="G72:G76"/>
-    <mergeCell ref="A77:A82"/>
-    <mergeCell ref="B77:B82"/>
-    <mergeCell ref="F77:F82"/>
-    <mergeCell ref="G77:G82"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="F88:F93"/>
-    <mergeCell ref="G88:G93"/>
-    <mergeCell ref="A104:A109"/>
-    <mergeCell ref="B104:B109"/>
-    <mergeCell ref="F104:F109"/>
-    <mergeCell ref="G104:G109"/>
-    <mergeCell ref="A65:A71"/>
-    <mergeCell ref="B65:B71"/>
-    <mergeCell ref="F65:F71"/>
-    <mergeCell ref="G65:G71"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="G94:G97"/>
-    <mergeCell ref="A98:A103"/>
-    <mergeCell ref="B98:B103"/>
-    <mergeCell ref="F98:F103"/>
+    <mergeCell ref="G204:G206"/>
+    <mergeCell ref="B207:B212"/>
+    <mergeCell ref="F207:F212"/>
+    <mergeCell ref="G207:G212"/>
+    <mergeCell ref="B204:B206"/>
+    <mergeCell ref="F204:F206"/>
+    <mergeCell ref="A198:A203"/>
+    <mergeCell ref="A204:A206"/>
+    <mergeCell ref="A207:A212"/>
+    <mergeCell ref="B198:B203"/>
+    <mergeCell ref="F198:F203"/>
+    <mergeCell ref="G198:G203"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
